--- a/skills/it-pianificazione-autonomi/assets/proiezione-pensione-autonomi.xlsx
+++ b/skills/it-pianificazione-autonomi/assets/proiezione-pensione-autonomi.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="157">
   <si>
     <t xml:space="preserve">Proiezione pensione autonomi — Parametri</t>
   </si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Montante fondo già accumulato</t>
   </si>
   <si>
-    <t xml:space="preserve">se hai già un fondo pensione</t>
+    <t xml:space="preserve">se hai già un fondo pensione; per la tassa in uscita è trattato come dedotto (stima prudente)</t>
   </si>
   <si>
     <t xml:space="preserve">Anni di iscrizione al fondo (al pensionamento)</t>
@@ -207,6 +207,27 @@
     <t xml:space="preserve">ridotto per i bienni mancanti; è quello usato</t>
   </si>
   <si>
+    <t xml:space="preserve">Fondo pensione: deducibilità e uscita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versamento dedotto ogni anno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forfettario puro: 0 (non deduce); ordinario: fino al plafond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non dedotti comunicati al fondo (1 = sì, 0 = no)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entro il 31/12 dell'anno dopo: così in uscita non sono tassati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plafond deducibilità fondo pensione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">art. 8 c. 4 D.Lgs. 252/2005 (€5.164,57 fino al 2025)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coefficienti di trasformazione — biennio 2025-2026</t>
   </si>
   <si>
@@ -351,10 +372,10 @@
     <t xml:space="preserve">in ingresso è ~zero (vedi riga evidenziata), perché l'imposta sostitutiva non è IRPEF. Il fondo</t>
   </si>
   <si>
-    <t xml:space="preserve">pensione resta utile al forfettario per la capitalizzazione e la tassazione finale agevolata (15→9%),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ma senza lo sconto in ingresso va confrontato con un PAC di ETF (più liquido). L'IRPEF mostrata è</t>
+    <t xml:space="preserve">pensione resta utile al forfettario per la capitalizzazione e perché i versamenti non dedotti, se</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comunicati al fondo, in uscita non sono tassati; va confrontato con un PAC di ETF (più liquido). L'IRPEF è</t>
   </si>
   <si>
     <t xml:space="preserve">lorda, ante detrazioni: l'imposta ordinaria reale è un po' più bassa. Confronto indicativo.</t>
@@ -369,6 +390,9 @@
     <t xml:space="preserve">Rendimento netto</t>
   </si>
   <si>
+    <t xml:space="preserve">Base tassabile in uscita (€ oggi)</t>
+  </si>
+  <si>
     <t xml:space="preserve">RISULTATI FONDO PENSIONE</t>
   </si>
   <si>
@@ -378,7 +402,7 @@
     <t xml:space="preserve">Totale versato (somma versamenti)</t>
   </si>
   <si>
-    <t xml:space="preserve">Tassa finale sui contributi (15→9%)</t>
+    <t xml:space="preserve">Tassa finale (15→9%) sui versamenti dedotti</t>
   </si>
   <si>
     <t xml:space="preserve">Montante netto disponibile</t>
@@ -390,13 +414,13 @@
     <t xml:space="preserve">NOTA DEDUCIBILITÀ: in regime ORDINARIO i versamenti sono deducibili dall'IRPEF fino a €5.300/anno</t>
   </si>
   <si>
-    <t xml:space="preserve">(vedi foglio Fiscalità). In regime FORFETTARIO puro NON sono deducibili: il fondo pensione rende</t>
-  </si>
-  <si>
-    <t xml:space="preserve">solo per capitalizzazione e tassazione finale agevolata, non per lo sconto in ingresso.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La tassa finale qui è approssimata sull'intero versato; i rendimenti sono già tassati nel fondo (al 20%).</t>
+    <t xml:space="preserve">(vedi foglio Fiscalità). In FORFETTARIO puro non sono deducibili, ma se comunicati al fondo entro il 31/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dell'anno dopo in uscita non sono tassati: il fondo rende per capitalizzazione e uscita esente su quella parte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tassa finale solo sui versamenti dedotti (e sui non dedotti NON comunicati); rendimenti già tassati esclusi (art. 11 c. 6).</t>
   </si>
   <si>
     <t xml:space="preserve">Riepilogo: pensione attesa e gap</t>
@@ -876,34 +900,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1048,8 +1072,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C48"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
@@ -1403,8 +1427,49 @@
         <v>59</v>
       </c>
     </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" s="11" t="n">
+        <f aca="false">IF(Input!$B$19=1,0,MIN(Input!$B$28,Input!$B$48))</f>
+        <v>0</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="10" t="n">
+        <v>5300</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:C4"/>
@@ -1413,6 +1478,7 @@
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A45:C45"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B11" type="list">
@@ -1440,7 +1506,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
@@ -1448,27 +1514,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1638,12 +1704,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
@@ -1651,7 +1717,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -1659,7 +1725,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -1667,7 +1733,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -1698,7 +1764,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G63"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
@@ -1710,7 +1776,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1721,7 +1787,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1732,25 +1798,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3205,7 +3271,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3216,7 +3282,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B58" s="25" t="n">
         <f aca="false">INDEX(G5:G54,MATCH(Input!$B$6-1,B5:B54,0))</f>
@@ -3225,7 +3291,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B59" s="26" t="n">
         <f aca="false">Input!$B$43</f>
@@ -3234,7 +3300,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B60" s="27" t="n">
         <f aca="false">B58*B59</f>
@@ -3243,7 +3309,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B61" s="25" t="n">
         <f aca="false">B60/13</f>
@@ -3252,7 +3318,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B62" s="25" t="n">
         <f aca="false">Input!$B$23*(1+Input!$B$24)^(Input!$B$7-1)</f>
@@ -3261,7 +3327,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B63" s="28" t="n">
         <f aca="false">IF(B62&gt;0,B60/B62,0)</f>
@@ -3290,7 +3356,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="15"/>
@@ -3299,7 +3365,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3307,7 +3373,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3315,18 +3381,18 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B5" s="23" t="n">
         <f aca="false">Input!$B$21</f>
@@ -3350,12 +3416,12 @@
         <v>40000</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B7" s="23" t="n">
         <f aca="false">B6*Input!$B$12</f>
@@ -3366,12 +3432,12 @@
         <v>10428</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B8" s="23" t="n">
         <f aca="false">MIN(Input!$B$28,5300)*0</f>
@@ -3382,12 +3448,12 @@
         <v>0</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">MAX(0,B6-B7-B8)</f>
@@ -3400,7 +3466,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B10" s="23" t="n">
         <f aca="false">B9*Input!$B$36</f>
@@ -3411,12 +3477,12 @@
         <v>6958.76</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B11" s="30" t="n">
         <f aca="false">B6-B7-B10</f>
@@ -3429,7 +3495,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -3437,7 +3503,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B14" s="23" t="n">
         <f aca="false">MAX(0,B6-B7)*Input!$B$36</f>
@@ -3450,7 +3516,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B15" s="31" t="n">
         <f aca="false">B14-B10</f>
@@ -3461,12 +3527,12 @@
         <v>0</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B17" s="32"/>
       <c r="C17" s="32"/>
@@ -3474,7 +3540,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="32"/>
@@ -3482,7 +3548,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="32" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="32"/>
@@ -3490,7 +3556,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="32"/>
@@ -3498,7 +3564,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
@@ -3506,7 +3572,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="32"/>
@@ -3514,7 +3580,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="32"/>
@@ -3548,12 +3614,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G67"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3568,7 +3635,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3578,22 +3645,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>77</v>
+        <v>84</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3620,6 +3690,10 @@
         <f aca="false">IF(B5&lt;Input!$B$6,D5+C5+E5,D5)</f>
         <v>0</v>
       </c>
+      <c r="G5" s="23" t="n">
+        <f aca="false">IF(B5&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C5-Input!$B$46))*(1+Input!$B$39)^(A5-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="n">
@@ -3645,6 +3719,10 @@
         <f aca="false">IF(B6&lt;Input!$B$6,D6+C6+E6,D6)</f>
         <v>0</v>
       </c>
+      <c r="G6" s="23" t="n">
+        <f aca="false">IF(B6&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C6-Input!$B$46))*(1+Input!$B$39)^(A6-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="n">
@@ -3670,6 +3748,10 @@
         <f aca="false">IF(B7&lt;Input!$B$6,D7+C7+E7,D7)</f>
         <v>0</v>
       </c>
+      <c r="G7" s="23" t="n">
+        <f aca="false">IF(B7&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C7-Input!$B$46))*(1+Input!$B$39)^(A7-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="n">
@@ -3695,6 +3777,10 @@
         <f aca="false">IF(B8&lt;Input!$B$6,D8+C8+E8,D8)</f>
         <v>0</v>
       </c>
+      <c r="G8" s="23" t="n">
+        <f aca="false">IF(B8&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C8-Input!$B$46))*(1+Input!$B$39)^(A8-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="n">
@@ -3720,6 +3806,10 @@
         <f aca="false">IF(B9&lt;Input!$B$6,D9+C9+E9,D9)</f>
         <v>0</v>
       </c>
+      <c r="G9" s="23" t="n">
+        <f aca="false">IF(B9&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C9-Input!$B$46))*(1+Input!$B$39)^(A9-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="n">
@@ -3745,6 +3835,10 @@
         <f aca="false">IF(B10&lt;Input!$B$6,D10+C10+E10,D10)</f>
         <v>0</v>
       </c>
+      <c r="G10" s="23" t="n">
+        <f aca="false">IF(B10&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C10-Input!$B$46))*(1+Input!$B$39)^(A10-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="n">
@@ -3770,6 +3864,10 @@
         <f aca="false">IF(B11&lt;Input!$B$6,D11+C11+E11,D11)</f>
         <v>0</v>
       </c>
+      <c r="G11" s="23" t="n">
+        <f aca="false">IF(B11&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C11-Input!$B$46))*(1+Input!$B$39)^(A11-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="n">
@@ -3795,6 +3893,10 @@
         <f aca="false">IF(B12&lt;Input!$B$6,D12+C12+E12,D12)</f>
         <v>0</v>
       </c>
+      <c r="G12" s="23" t="n">
+        <f aca="false">IF(B12&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C12-Input!$B$46))*(1+Input!$B$39)^(A12-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="n">
@@ -3820,6 +3922,10 @@
         <f aca="false">IF(B13&lt;Input!$B$6,D13+C13+E13,D13)</f>
         <v>0</v>
       </c>
+      <c r="G13" s="23" t="n">
+        <f aca="false">IF(B13&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C13-Input!$B$46))*(1+Input!$B$39)^(A13-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="n">
@@ -3845,6 +3951,10 @@
         <f aca="false">IF(B14&lt;Input!$B$6,D14+C14+E14,D14)</f>
         <v>0</v>
       </c>
+      <c r="G14" s="23" t="n">
+        <f aca="false">IF(B14&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C14-Input!$B$46))*(1+Input!$B$39)^(A14-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="n">
@@ -3870,6 +3980,10 @@
         <f aca="false">IF(B15&lt;Input!$B$6,D15+C15+E15,D15)</f>
         <v>0</v>
       </c>
+      <c r="G15" s="23" t="n">
+        <f aca="false">IF(B15&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C15-Input!$B$46))*(1+Input!$B$39)^(A15-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="n">
@@ -3895,6 +4009,10 @@
         <f aca="false">IF(B16&lt;Input!$B$6,D16+C16+E16,D16)</f>
         <v>0</v>
       </c>
+      <c r="G16" s="23" t="n">
+        <f aca="false">IF(B16&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C16-Input!$B$46))*(1+Input!$B$39)^(A16-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="n">
@@ -3920,6 +4038,10 @@
         <f aca="false">IF(B17&lt;Input!$B$6,D17+C17+E17,D17)</f>
         <v>0</v>
       </c>
+      <c r="G17" s="23" t="n">
+        <f aca="false">IF(B17&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C17-Input!$B$46))*(1+Input!$B$39)^(A17-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="n">
@@ -3945,6 +4067,10 @@
         <f aca="false">IF(B18&lt;Input!$B$6,D18+C18+E18,D18)</f>
         <v>0</v>
       </c>
+      <c r="G18" s="23" t="n">
+        <f aca="false">IF(B18&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C18-Input!$B$46))*(1+Input!$B$39)^(A18-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="n">
@@ -3970,6 +4096,10 @@
         <f aca="false">IF(B19&lt;Input!$B$6,D19+C19+E19,D19)</f>
         <v>0</v>
       </c>
+      <c r="G19" s="23" t="n">
+        <f aca="false">IF(B19&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C19-Input!$B$46))*(1+Input!$B$39)^(A19-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="n">
@@ -3995,6 +4125,10 @@
         <f aca="false">IF(B20&lt;Input!$B$6,D20+C20+E20,D20)</f>
         <v>0</v>
       </c>
+      <c r="G20" s="23" t="n">
+        <f aca="false">IF(B20&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C20-Input!$B$46))*(1+Input!$B$39)^(A20-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="n">
@@ -4020,6 +4154,10 @@
         <f aca="false">IF(B21&lt;Input!$B$6,D21+C21+E21,D21)</f>
         <v>0</v>
       </c>
+      <c r="G21" s="23" t="n">
+        <f aca="false">IF(B21&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C21-Input!$B$46))*(1+Input!$B$39)^(A21-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="n">
@@ -4045,6 +4183,10 @@
         <f aca="false">IF(B22&lt;Input!$B$6,D22+C22+E22,D22)</f>
         <v>0</v>
       </c>
+      <c r="G22" s="23" t="n">
+        <f aca="false">IF(B22&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C22-Input!$B$46))*(1+Input!$B$39)^(A22-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="n">
@@ -4070,6 +4212,10 @@
         <f aca="false">IF(B23&lt;Input!$B$6,D23+C23+E23,D23)</f>
         <v>0</v>
       </c>
+      <c r="G23" s="23" t="n">
+        <f aca="false">IF(B23&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C23-Input!$B$46))*(1+Input!$B$39)^(A23-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="n">
@@ -4095,6 +4241,10 @@
         <f aca="false">IF(B24&lt;Input!$B$6,D24+C24+E24,D24)</f>
         <v>0</v>
       </c>
+      <c r="G24" s="23" t="n">
+        <f aca="false">IF(B24&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C24-Input!$B$46))*(1+Input!$B$39)^(A24-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="n">
@@ -4120,6 +4270,10 @@
         <f aca="false">IF(B25&lt;Input!$B$6,D25+C25+E25,D25)</f>
         <v>0</v>
       </c>
+      <c r="G25" s="23" t="n">
+        <f aca="false">IF(B25&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C25-Input!$B$46))*(1+Input!$B$39)^(A25-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="n">
@@ -4145,6 +4299,10 @@
         <f aca="false">IF(B26&lt;Input!$B$6,D26+C26+E26,D26)</f>
         <v>0</v>
       </c>
+      <c r="G26" s="23" t="n">
+        <f aca="false">IF(B26&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C26-Input!$B$46))*(1+Input!$B$39)^(A26-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="n">
@@ -4170,6 +4328,10 @@
         <f aca="false">IF(B27&lt;Input!$B$6,D27+C27+E27,D27)</f>
         <v>0</v>
       </c>
+      <c r="G27" s="23" t="n">
+        <f aca="false">IF(B27&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C27-Input!$B$46))*(1+Input!$B$39)^(A27-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="n">
@@ -4195,6 +4357,10 @@
         <f aca="false">IF(B28&lt;Input!$B$6,D28+C28+E28,D28)</f>
         <v>0</v>
       </c>
+      <c r="G28" s="23" t="n">
+        <f aca="false">IF(B28&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C28-Input!$B$46))*(1+Input!$B$39)^(A28-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="n">
@@ -4220,6 +4386,10 @@
         <f aca="false">IF(B29&lt;Input!$B$6,D29+C29+E29,D29)</f>
         <v>0</v>
       </c>
+      <c r="G29" s="23" t="n">
+        <f aca="false">IF(B29&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C29-Input!$B$46))*(1+Input!$B$39)^(A29-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="n">
@@ -4245,6 +4415,10 @@
         <f aca="false">IF(B30&lt;Input!$B$6,D30+C30+E30,D30)</f>
         <v>0</v>
       </c>
+      <c r="G30" s="23" t="n">
+        <f aca="false">IF(B30&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C30-Input!$B$46))*(1+Input!$B$39)^(A30-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="n">
@@ -4270,6 +4444,10 @@
         <f aca="false">IF(B31&lt;Input!$B$6,D31+C31+E31,D31)</f>
         <v>0</v>
       </c>
+      <c r="G31" s="23" t="n">
+        <f aca="false">IF(B31&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C31-Input!$B$46))*(1+Input!$B$39)^(A31-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="n">
@@ -4295,6 +4473,10 @@
         <f aca="false">IF(B32&lt;Input!$B$6,D32+C32+E32,D32)</f>
         <v>0</v>
       </c>
+      <c r="G32" s="23" t="n">
+        <f aca="false">IF(B32&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C32-Input!$B$46))*(1+Input!$B$39)^(A32-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="n">
@@ -4320,6 +4502,10 @@
         <f aca="false">IF(B33&lt;Input!$B$6,D33+C33+E33,D33)</f>
         <v>0</v>
       </c>
+      <c r="G33" s="23" t="n">
+        <f aca="false">IF(B33&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C33-Input!$B$46))*(1+Input!$B$39)^(A33-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="n">
@@ -4345,6 +4531,10 @@
         <f aca="false">IF(B34&lt;Input!$B$6,D34+C34+E34,D34)</f>
         <v>0</v>
       </c>
+      <c r="G34" s="23" t="n">
+        <f aca="false">IF(B34&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C34-Input!$B$46))*(1+Input!$B$39)^(A34-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="n">
@@ -4370,6 +4560,10 @@
         <f aca="false">IF(B35&lt;Input!$B$6,D35+C35+E35,D35)</f>
         <v>0</v>
       </c>
+      <c r="G35" s="23" t="n">
+        <f aca="false">IF(B35&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C35-Input!$B$46))*(1+Input!$B$39)^(A35-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="n">
@@ -4395,6 +4589,10 @@
         <f aca="false">IF(B36&lt;Input!$B$6,D36+C36+E36,D36)</f>
         <v>0</v>
       </c>
+      <c r="G36" s="23" t="n">
+        <f aca="false">IF(B36&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C36-Input!$B$46))*(1+Input!$B$39)^(A36-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="n">
@@ -4420,6 +4618,10 @@
         <f aca="false">IF(B37&lt;Input!$B$6,D37+C37+E37,D37)</f>
         <v>0</v>
       </c>
+      <c r="G37" s="23" t="n">
+        <f aca="false">IF(B37&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C37-Input!$B$46))*(1+Input!$B$39)^(A37-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="n">
@@ -4445,6 +4647,10 @@
         <f aca="false">IF(B38&lt;Input!$B$6,D38+C38+E38,D38)</f>
         <v>0</v>
       </c>
+      <c r="G38" s="23" t="n">
+        <f aca="false">IF(B38&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C38-Input!$B$46))*(1+Input!$B$39)^(A38-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="n">
@@ -4470,6 +4676,10 @@
         <f aca="false">IF(B39&lt;Input!$B$6,D39+C39+E39,D39)</f>
         <v>0</v>
       </c>
+      <c r="G39" s="23" t="n">
+        <f aca="false">IF(B39&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C39-Input!$B$46))*(1+Input!$B$39)^(A39-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="n">
@@ -4495,6 +4705,10 @@
         <f aca="false">IF(B40&lt;Input!$B$6,D40+C40+E40,D40)</f>
         <v>0</v>
       </c>
+      <c r="G40" s="23" t="n">
+        <f aca="false">IF(B40&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C40-Input!$B$46))*(1+Input!$B$39)^(A40-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="n">
@@ -4520,6 +4734,10 @@
         <f aca="false">IF(B41&lt;Input!$B$6,D41+C41+E41,D41)</f>
         <v>0</v>
       </c>
+      <c r="G41" s="23" t="n">
+        <f aca="false">IF(B41&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C41-Input!$B$46))*(1+Input!$B$39)^(A41-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="n">
@@ -4545,6 +4763,10 @@
         <f aca="false">IF(B42&lt;Input!$B$6,D42+C42+E42,D42)</f>
         <v>0</v>
       </c>
+      <c r="G42" s="23" t="n">
+        <f aca="false">IF(B42&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C42-Input!$B$46))*(1+Input!$B$39)^(A42-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="n">
@@ -4570,6 +4792,10 @@
         <f aca="false">IF(B43&lt;Input!$B$6,D43+C43+E43,D43)</f>
         <v>0</v>
       </c>
+      <c r="G43" s="23" t="n">
+        <f aca="false">IF(B43&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C43-Input!$B$46))*(1+Input!$B$39)^(A43-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="n">
@@ -4595,6 +4821,10 @@
         <f aca="false">IF(B44&lt;Input!$B$6,D44+C44+E44,D44)</f>
         <v>0</v>
       </c>
+      <c r="G44" s="23" t="n">
+        <f aca="false">IF(B44&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C44-Input!$B$46))*(1+Input!$B$39)^(A44-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="n">
@@ -4620,6 +4850,10 @@
         <f aca="false">IF(B45&lt;Input!$B$6,D45+C45+E45,D45)</f>
         <v>0</v>
       </c>
+      <c r="G45" s="23" t="n">
+        <f aca="false">IF(B45&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C45-Input!$B$46))*(1+Input!$B$39)^(A45-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="n">
@@ -4645,6 +4879,10 @@
         <f aca="false">IF(B46&lt;Input!$B$6,D46+C46+E46,D46)</f>
         <v>0</v>
       </c>
+      <c r="G46" s="23" t="n">
+        <f aca="false">IF(B46&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C46-Input!$B$46))*(1+Input!$B$39)^(A46-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="n">
@@ -4670,6 +4908,10 @@
         <f aca="false">IF(B47&lt;Input!$B$6,D47+C47+E47,D47)</f>
         <v>0</v>
       </c>
+      <c r="G47" s="23" t="n">
+        <f aca="false">IF(B47&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C47-Input!$B$46))*(1+Input!$B$39)^(A47-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="21" t="n">
@@ -4695,6 +4937,10 @@
         <f aca="false">IF(B48&lt;Input!$B$6,D48+C48+E48,D48)</f>
         <v>0</v>
       </c>
+      <c r="G48" s="23" t="n">
+        <f aca="false">IF(B48&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C48-Input!$B$46))*(1+Input!$B$39)^(A48-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="21" t="n">
@@ -4720,6 +4966,10 @@
         <f aca="false">IF(B49&lt;Input!$B$6,D49+C49+E49,D49)</f>
         <v>0</v>
       </c>
+      <c r="G49" s="23" t="n">
+        <f aca="false">IF(B49&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C49-Input!$B$46))*(1+Input!$B$39)^(A49-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="21" t="n">
@@ -4745,6 +4995,10 @@
         <f aca="false">IF(B50&lt;Input!$B$6,D50+C50+E50,D50)</f>
         <v>0</v>
       </c>
+      <c r="G50" s="23" t="n">
+        <f aca="false">IF(B50&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C50-Input!$B$46))*(1+Input!$B$39)^(A50-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="21" t="n">
@@ -4770,6 +5024,10 @@
         <f aca="false">IF(B51&lt;Input!$B$6,D51+C51+E51,D51)</f>
         <v>0</v>
       </c>
+      <c r="G51" s="23" t="n">
+        <f aca="false">IF(B51&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C51-Input!$B$46))*(1+Input!$B$39)^(A51-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="21" t="n">
@@ -4795,6 +5053,10 @@
         <f aca="false">IF(B52&lt;Input!$B$6,D52+C52+E52,D52)</f>
         <v>0</v>
       </c>
+      <c r="G52" s="23" t="n">
+        <f aca="false">IF(B52&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C52-Input!$B$46))*(1+Input!$B$39)^(A52-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="21" t="n">
@@ -4820,6 +5082,10 @@
         <f aca="false">IF(B53&lt;Input!$B$6,D53+C53+E53,D53)</f>
         <v>0</v>
       </c>
+      <c r="G53" s="23" t="n">
+        <f aca="false">IF(B53&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C53-Input!$B$46))*(1+Input!$B$39)^(A53-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="21" t="n">
@@ -4845,10 +5111,14 @@
         <f aca="false">IF(B54&lt;Input!$B$6,D54+C54+E54,D54)</f>
         <v>0</v>
       </c>
+      <c r="G54" s="23" t="n">
+        <f aca="false">IF(B54&lt;Input!$B$6,(Input!$B$46+IF(Input!$B$47=1,0,C54-Input!$B$46))*(1+Input!$B$39)^(A54-Input!$B$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -4858,7 +5128,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B58" s="25" t="n">
         <f aca="false">INDEX(F5:F54,MATCH(Input!$B$6-1,B5:B54,0))</f>
@@ -4867,7 +5137,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B59" s="25" t="n">
         <f aca="false">Input!$B$31+SUMIF(B5:B54,"&lt;"&amp;Input!$B$6,C5:C54)</f>
@@ -4876,16 +5146,16 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B60" s="25" t="n">
-        <f aca="false">B59*Input!$B$38</f>
+        <f aca="false">(Input!$B$31*(1+Input!$B$39)^(-Input!$B$7)+SUM(G5:G54))*Input!$B$38</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B61" s="27" t="n">
         <f aca="false">B58-B60</f>
@@ -4894,7 +5164,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B62" s="11" t="n">
         <f aca="false">B61*Input!$B$43</f>
@@ -4903,7 +5173,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="32" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B64" s="32"/>
       <c r="C64" s="32"/>
@@ -4913,7 +5183,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="32" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B65" s="32"/>
       <c r="C65" s="32"/>
@@ -4923,7 +5193,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="32" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B66" s="32"/>
       <c r="C66" s="32"/>
@@ -4933,7 +5203,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="32" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B67" s="32"/>
       <c r="C67" s="32"/>
@@ -4967,7 +5237,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
@@ -4977,7 +5247,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4985,7 +5255,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4993,7 +5263,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -5010,7 +5280,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B6" s="25" t="n">
         <f aca="false">Complementare!B62</f>
@@ -5019,7 +5289,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
@@ -5028,7 +5298,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">B7/13</f>
@@ -5037,7 +5307,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -5045,7 +5315,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">Previdenza!B62</f>
@@ -5054,7 +5324,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">IF(B11&gt;0,B5/B11,0)</f>
@@ -5063,7 +5333,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B13" s="28" t="n">
         <f aca="false">IF(B11&gt;0,B7/B11,0)</f>
@@ -5072,19 +5342,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B14" s="27" t="n">
         <f aca="false">MAX(0,B11-B7)</f>
         <v>23280.2172804025</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B15" s="25" t="n">
         <f aca="false">B14/13</f>
@@ -5093,7 +5363,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -5101,23 +5371,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B20" s="23" t="n">
         <f aca="false">B5</f>
@@ -5130,7 +5400,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="33" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B21" s="23" t="n">
         <f aca="false">B7</f>
@@ -5143,7 +5413,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="32"/>
@@ -5151,7 +5421,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="32" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B24" s="32"/>
       <c r="C24" s="32"/>
@@ -5159,7 +5429,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="32" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
@@ -5167,7 +5437,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="32" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
@@ -5175,7 +5445,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="32" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B27" s="32"/>
       <c r="C27" s="32"/>

--- a/skills/it-pianificazione-autonomi/assets/proiezione-pensione-autonomi.xlsx
+++ b/skills/it-pianificazione-autonomi/assets/proiezione-pensione-autonomi.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="189">
   <si>
     <t xml:space="preserve">Proiezione pensione autonomi — Parametri</t>
   </si>
@@ -78,10 +78,10 @@
     <t xml:space="preserve">stima del montante contributivo a oggi</t>
   </si>
   <si>
-    <t xml:space="preserve">Rivalutazione annua del montante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INPS: media PIL 5 anni; cassa: regola propria (reale)</t>
+    <t xml:space="preserve">Rivalutazione annua del montante (reale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gestione Separata: PIL reale ~0,5%, come i dipendenti; cassa: regola propria al netto dell'inflazione</t>
   </si>
   <si>
     <t xml:space="preserve">Decadimento coefficiente / biennio</t>
@@ -213,7 +213,7 @@
     <t xml:space="preserve">Versamento dedotto ogni anno</t>
   </si>
   <si>
-    <t xml:space="preserve">forfettario puro: 0 (non deduce); ordinario: fino al plafond</t>
+    <t xml:space="preserve">forfettario: solo fino agli altri redditi IRPEF (B52); ordinario: fino al plafond</t>
   </si>
   <si>
     <t xml:space="preserve">Non dedotti comunicati al fondo (1 = sì, 0 = no)</t>
@@ -228,6 +228,39 @@
     <t xml:space="preserve">art. 8 c. 4 D.Lgs. 252/2005 (€5.164,57 fino al 2025)</t>
   </si>
   <si>
+    <t xml:space="preserve">Massimale, altri redditi e spese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massimale contributivo annuo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gestione Separata 2026 (Circ. INPS 8/2026); per una cassa il suo tetto, qui trattato come tetto secco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Altri redditi IRPEF (no cedolare secca)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">affitti a IRPEF, lavoro dipendente part-time: danno capienza alla deduzione del fondo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spesa mensile attuale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€/mese, in euro di oggi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fattore riduzione spesa post-pensione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tipico 0,75-0,85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spesa annua target (€ di oggi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spesa mensile × 12 × fattore</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coefficienti di trasformazione — biennio 2025-2026</t>
   </si>
   <si>
@@ -261,7 +294,7 @@
     <t xml:space="preserve">Proiezione previdenza obbligatoria (Gestione Separata / cassa)</t>
   </si>
   <si>
-    <t xml:space="preserve">Montante contributivo anno per anno. La pensione usa il coefficiente PROIETTATO al pensionamento (foglio Input). Tutto in termini reali (euro di oggi).</t>
+    <t xml:space="preserve">Montante contributivo anno per anno, in euro di oggi: contributi fino al massimale, rivalutazione dall'anno dopo il versamento (L. 335/1995). La pensione usa il coefficiente PROIETTATO al pensionamento (foglio Input).</t>
   </si>
   <si>
     <t xml:space="preserve">Anno</t>
@@ -270,7 +303,7 @@
     <t xml:space="preserve">Reddito</t>
   </si>
   <si>
-    <t xml:space="preserve">Contributo a montante</t>
+    <t xml:space="preserve">Contributo a montante (fino al massimale)</t>
   </si>
   <si>
     <t xml:space="preserve">Montante inizio</t>
@@ -303,6 +336,21 @@
     <t xml:space="preserve">Tasso di sostituzione lordo</t>
   </si>
   <si>
+    <t xml:space="preserve">IRPEF lorda sulla pensione (scaglioni 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detrazione pensionati (art. 13 c. 3 TUIR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addizionali regionali + comunali (~2%, se c'è IRPEF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pensione obbligatoria NETTA annua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pensione obbligatoria NETTA mensile (×13)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fiscalità annua — forfettario vs ordinario</t>
   </si>
   <si>
@@ -330,22 +378,22 @@
     <t xml:space="preserve">DEDUCIBILI in entrambi i regimi</t>
   </si>
   <si>
-    <t xml:space="preserve">− Versamento fondo pensione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deducibile SOLO in ordinario (forf.: 0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reddito imponibile (netto contributi)</t>
+    <t xml:space="preserve">− Versamento fondo pensione dedotto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forf.: solo dagli altri redditi IRPEF; ord.: dal reddito complessivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imponibile (forf.: sostitutiva; ord.: IRPEF con altri redditi)</t>
   </si>
   <si>
     <t xml:space="preserve">Imposta</t>
   </si>
   <si>
-    <t xml:space="preserve">forf.: sostitutiva; ord.: IRPEF lorda (ante detrazioni)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netto disponibile (reddito − contributi − imposta)</t>
+    <t xml:space="preserve">forf.: sostitutiva + IRPEF lorda sugli altri redditi; ord.: IRPEF lorda (ante detrazioni)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netto disponibile (redditi − contributi − imposte)</t>
   </si>
   <si>
     <t xml:space="preserve">Beneficio fiscale del versamento al fondo pensione</t>
@@ -357,7 +405,7 @@
     <t xml:space="preserve">Risparmio fiscale dal fondo pensione</t>
   </si>
   <si>
-    <t xml:space="preserve">forf.: ~0 (deduzione inefficace); ord.: aliquota×versamento</t>
+    <t xml:space="preserve">forf.: IRPEF risparmiata sugli altri redditi; ord.: aliquota × versamento</t>
   </si>
   <si>
     <t xml:space="preserve">LETTURA: i contributi previdenziali OBBLIGATORI (Gestione Separata o cassa) si deducono in entrambi</t>
@@ -366,10 +414,10 @@
     <t xml:space="preserve">i regimi e abbattono l'imponibile. Il versamento VOLONTARIO al fondo pensione complementare invece</t>
   </si>
   <si>
-    <t xml:space="preserve">è deducibile solo in regime ORDINARIO (contro l'IRPEF): per un forfettario puro il risparmio fiscale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">in ingresso è ~zero (vedi riga evidenziata), perché l'imposta sostitutiva non è IRPEF. Il fondo</t>
+    <t xml:space="preserve">si deduce solo contro l'IRPEF: in ORDINARIO fino al plafond, in forfettario solo fino agli altri redditi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRPEF (Input B52). Per un forfettario puro il risparmio in ingresso è zero (riga evidenziata). Il fondo</t>
   </si>
   <si>
     <t xml:space="preserve">pensione resta utile al forfettario per la capitalizzazione e perché i versamenti non dedotti, se</t>
@@ -426,7 +474,7 @@
     <t xml:space="preserve">Riepilogo: pensione attesa e gap</t>
   </si>
   <si>
-    <t xml:space="preserve">Somma di previdenza obbligatoria e complementare, tasso di sostituzione e gap rispetto al reddito attuale. Valori in euro di oggi (reali).</t>
+    <t xml:space="preserve">Previdenza obbligatoria e complementare, tasso di sostituzione, gap rispetto al reddito attuale e alla spesa target. Valori in euro di oggi (reali).</t>
   </si>
   <si>
     <t xml:space="preserve">Pensione attesa (annua, lorda)</t>
@@ -441,6 +489,9 @@
     <t xml:space="preserve">Pensione totale mensile (×13)</t>
   </si>
   <si>
+    <t xml:space="preserve">Pensione totale NETTA annua</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tasso di sostituzione e gap</t>
   </si>
   <si>
@@ -462,7 +513,7 @@
     <t xml:space="preserve">Gap mensile (×13)</t>
   </si>
   <si>
-    <t xml:space="preserve">Scenari</t>
+    <t xml:space="preserve">Obbligatoria e complementare (lorde)</t>
   </si>
   <si>
     <t xml:space="preserve">Tasso di sostituzione obbligatoria + complementare</t>
@@ -496,6 +547,51 @@
   </si>
   <si>
     <t xml:space="preserve">Valori reali (euro di oggi); proiezione indicativa, non una garanzia. Non è consulenza.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenari: gap rispetto alla spesa target (€ di oggi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Come proiezione-tenore-vita.md: gap = spesa target − pensione netta. Base = fogli di calcolo; le altre colonne ricalcolano con i propri parametri.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conservativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ottimistico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rivalutazione montante (reale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rendimento netto fondo (reale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pensione obbligatoria lorda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pensione obbligatoria netta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rendita fondo (netta della tassa in uscita)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pensione totale netta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spesa target annua (€ di oggi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP (spesa target − pensione netta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap % della spesa target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenari indicativi in euro di oggi; per le casse la rivalutazione segue la regola della cassa. Non è consulenza.</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1168,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
@@ -1185,7 +1281,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>18</v>
@@ -1439,7 +1535,7 @@
         <v>61</v>
       </c>
       <c r="B46" s="11" t="n">
-        <f aca="false">IF(Input!$B$19=1,0,MIN(Input!$B$28,Input!$B$48))</f>
+        <f aca="false">IF(Input!$B$19=1,MIN(Input!$B$28,Input!$B$48,Input!$B$52),MIN(Input!$B$28,Input!$B$48))</f>
         <v>0</v>
       </c>
       <c r="C46" s="7" t="s">
@@ -1468,8 +1564,71 @@
         <v>66</v>
       </c>
     </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" s="10" t="n">
+        <v>122295</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B53" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B54" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B55" s="11" t="n">
+        <f aca="false">Input!$B$53*12*Input!$B$54</f>
+        <v>18720</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:C4"/>
@@ -1479,6 +1638,7 @@
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A50:C50"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B11" type="list">
@@ -1514,27 +1674,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1704,12 +1864,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
@@ -1717,7 +1877,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -1725,7 +1885,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -1733,7 +1893,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -1763,7 +1923,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="8"/>
@@ -1776,7 +1936,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1787,7 +1947,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1798,25 +1958,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1832,7 +1992,7 @@
         <v>31200</v>
       </c>
       <c r="D5" s="23" t="n">
-        <f aca="false">C5*Input!$B$12</f>
+        <f aca="false">MIN(C5,Input!$B$51)*Input!$B$12</f>
         <v>8133.84</v>
       </c>
       <c r="E5" s="24" t="n">
@@ -1840,12 +2000,12 @@
         <v>25000</v>
       </c>
       <c r="F5" s="23" t="n">
-        <f aca="false">(E5+D5)*Input!$B$14</f>
-        <v>662.6768</v>
+        <f aca="false">E5*Input!$B$14</f>
+        <v>125</v>
       </c>
       <c r="G5" s="23" t="n">
         <f aca="false">IF(B5&lt;Input!$B$6,E5+D5+F5,E5)</f>
-        <v>33796.5168</v>
+        <v>33258.84</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,20 +2021,20 @@
         <v>31512</v>
       </c>
       <c r="D6" s="23" t="n">
-        <f aca="false">C6*Input!$B$12</f>
+        <f aca="false">MIN(C6,Input!$B$51)*Input!$B$12</f>
         <v>8215.1784</v>
       </c>
       <c r="E6" s="23" t="n">
         <f aca="false">G5</f>
-        <v>33796.5168</v>
+        <v>33258.84</v>
       </c>
       <c r="F6" s="23" t="n">
-        <f aca="false">(E6+D6)*Input!$B$14</f>
-        <v>840.233904</v>
+        <f aca="false">E6*Input!$B$14</f>
+        <v>166.2942</v>
       </c>
       <c r="G6" s="23" t="n">
         <f aca="false">IF(B6&lt;Input!$B$6,E6+D6+F6,E6)</f>
-        <v>42851.929104</v>
+        <v>41640.3126</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1890,20 +2050,20 @@
         <v>31827.12</v>
       </c>
       <c r="D7" s="23" t="n">
-        <f aca="false">C7*Input!$B$12</f>
+        <f aca="false">MIN(C7,Input!$B$51)*Input!$B$12</f>
         <v>8297.330184</v>
       </c>
       <c r="E7" s="23" t="n">
         <f aca="false">G6</f>
-        <v>42851.929104</v>
+        <v>41640.3126</v>
       </c>
       <c r="F7" s="23" t="n">
-        <f aca="false">(E7+D7)*Input!$B$14</f>
-        <v>1022.98518576</v>
+        <f aca="false">E7*Input!$B$14</f>
+        <v>208.201563</v>
       </c>
       <c r="G7" s="23" t="n">
         <f aca="false">IF(B7&lt;Input!$B$6,E7+D7+F7,E7)</f>
-        <v>52172.24447376</v>
+        <v>50145.844347</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,20 +2079,20 @@
         <v>32145.3912</v>
       </c>
       <c r="D8" s="23" t="n">
-        <f aca="false">C8*Input!$B$12</f>
+        <f aca="false">MIN(C8,Input!$B$51)*Input!$B$12</f>
         <v>8380.30348584</v>
       </c>
       <c r="E8" s="23" t="n">
         <f aca="false">G7</f>
-        <v>52172.24447376</v>
+        <v>50145.844347</v>
       </c>
       <c r="F8" s="23" t="n">
-        <f aca="false">(E8+D8)*Input!$B$14</f>
-        <v>1211.050959192</v>
+        <f aca="false">E8*Input!$B$14</f>
+        <v>250.729221735</v>
       </c>
       <c r="G8" s="23" t="n">
         <f aca="false">IF(B8&lt;Input!$B$6,E8+D8+F8,E8)</f>
-        <v>61763.598918792</v>
+        <v>58776.877054575</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1948,20 +2108,20 @@
         <v>32466.845112</v>
       </c>
       <c r="D9" s="23" t="n">
-        <f aca="false">C9*Input!$B$12</f>
+        <f aca="false">MIN(C9,Input!$B$51)*Input!$B$12</f>
         <v>8464.1065206984</v>
       </c>
       <c r="E9" s="23" t="n">
         <f aca="false">G8</f>
-        <v>61763.598918792</v>
+        <v>58776.877054575</v>
       </c>
       <c r="F9" s="23" t="n">
-        <f aca="false">(E9+D9)*Input!$B$14</f>
-        <v>1404.55410878981</v>
+        <f aca="false">E9*Input!$B$14</f>
+        <v>293.884385272875</v>
       </c>
       <c r="G9" s="23" t="n">
         <f aca="false">IF(B9&lt;Input!$B$6,E9+D9+F9,E9)</f>
-        <v>71632.2595482802</v>
+        <v>67534.8679605463</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,20 +2137,20 @@
         <v>32791.51356312</v>
       </c>
       <c r="D10" s="23" t="n">
-        <f aca="false">C10*Input!$B$12</f>
+        <f aca="false">MIN(C10,Input!$B$51)*Input!$B$12</f>
         <v>8548.74758590539</v>
       </c>
       <c r="E10" s="23" t="n">
         <f aca="false">G9</f>
-        <v>71632.2595482802</v>
+        <v>67534.8679605463</v>
       </c>
       <c r="F10" s="23" t="n">
-        <f aca="false">(E10+D10)*Input!$B$14</f>
-        <v>1603.62014268371</v>
+        <f aca="false">E10*Input!$B$14</f>
+        <v>337.674339802731</v>
       </c>
       <c r="G10" s="23" t="n">
         <f aca="false">IF(B10&lt;Input!$B$6,E10+D10+F10,E10)</f>
-        <v>81784.6272768693</v>
+        <v>76421.2898862544</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2006,20 +2166,20 @@
         <v>33119.4286987512</v>
       </c>
       <c r="D11" s="23" t="n">
-        <f aca="false">C11*Input!$B$12</f>
+        <f aca="false">MIN(C11,Input!$B$51)*Input!$B$12</f>
         <v>8634.23506176444</v>
       </c>
       <c r="E11" s="23" t="n">
         <f aca="false">G10</f>
-        <v>81784.6272768693</v>
+        <v>76421.2898862544</v>
       </c>
       <c r="F11" s="23" t="n">
-        <f aca="false">(E11+D11)*Input!$B$14</f>
-        <v>1808.37724677267</v>
+        <f aca="false">E11*Input!$B$14</f>
+        <v>382.106449431272</v>
       </c>
       <c r="G11" s="23" t="n">
         <f aca="false">IF(B11&lt;Input!$B$6,E11+D11+F11,E11)</f>
-        <v>92227.2395854064</v>
+        <v>85437.6313974501</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2035,20 +2195,20 @@
         <v>33450.6229857387</v>
       </c>
       <c r="D12" s="23" t="n">
-        <f aca="false">C12*Input!$B$12</f>
+        <f aca="false">MIN(C12,Input!$B$51)*Input!$B$12</f>
         <v>8720.57741238208</v>
       </c>
       <c r="E12" s="23" t="n">
         <f aca="false">G11</f>
-        <v>92227.2395854064</v>
+        <v>85437.6313974501</v>
       </c>
       <c r="F12" s="23" t="n">
-        <f aca="false">(E12+D12)*Input!$B$14</f>
-        <v>2018.95633995577</v>
+        <f aca="false">E12*Input!$B$14</f>
+        <v>427.18815698725</v>
       </c>
       <c r="G12" s="23" t="n">
         <f aca="false">IF(B12&lt;Input!$B$6,E12+D12+F12,E12)</f>
-        <v>102966.773337744</v>
+        <v>94585.3969668194</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2064,20 +2224,20 @@
         <v>33785.1292155961</v>
       </c>
       <c r="D13" s="23" t="n">
-        <f aca="false">C13*Input!$B$12</f>
+        <f aca="false">MIN(C13,Input!$B$51)*Input!$B$12</f>
         <v>8807.78318650591</v>
       </c>
       <c r="E13" s="23" t="n">
         <f aca="false">G12</f>
-        <v>102966.773337744</v>
+        <v>94585.3969668194</v>
       </c>
       <c r="F13" s="23" t="n">
-        <f aca="false">(E13+D13)*Input!$B$14</f>
-        <v>2235.491130485</v>
+        <f aca="false">E13*Input!$B$14</f>
+        <v>472.926984834097</v>
       </c>
       <c r="G13" s="23" t="n">
         <f aca="false">IF(B13&lt;Input!$B$6,E13+D13+F13,E13)</f>
-        <v>114010.047654735</v>
+        <v>103866.107138159</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2093,20 +2253,20 @@
         <v>34122.9805077521</v>
       </c>
       <c r="D14" s="23" t="n">
-        <f aca="false">C14*Input!$B$12</f>
+        <f aca="false">MIN(C14,Input!$B$51)*Input!$B$12</f>
         <v>8895.86101837096</v>
       </c>
       <c r="E14" s="23" t="n">
         <f aca="false">G13</f>
-        <v>114010.047654735</v>
+        <v>103866.107138159</v>
       </c>
       <c r="F14" s="23" t="n">
-        <f aca="false">(E14+D14)*Input!$B$14</f>
-        <v>2458.11817346212</v>
+        <f aca="false">E14*Input!$B$14</f>
+        <v>519.330535690797</v>
       </c>
       <c r="G14" s="23" t="n">
         <f aca="false">IF(B14&lt;Input!$B$6,E14+D14+F14,E14)</f>
-        <v>125364.026846568</v>
+        <v>113281.298692221</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2122,20 +2282,20 @@
         <v>34464.2103128296</v>
       </c>
       <c r="D15" s="23" t="n">
-        <f aca="false">C15*Input!$B$12</f>
+        <f aca="false">MIN(C15,Input!$B$51)*Input!$B$12</f>
         <v>8984.81962855467</v>
       </c>
       <c r="E15" s="23" t="n">
         <f aca="false">G14</f>
-        <v>125364.026846568</v>
+        <v>113281.298692221</v>
       </c>
       <c r="F15" s="23" t="n">
-        <f aca="false">(E15+D15)*Input!$B$14</f>
-        <v>2686.97692950246</v>
+        <f aca="false">E15*Input!$B$14</f>
+        <v>566.406493461106</v>
       </c>
       <c r="G15" s="23" t="n">
         <f aca="false">IF(B15&lt;Input!$B$6,E15+D15+F15,E15)</f>
-        <v>137035.823404625</v>
+        <v>122832.524814237</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2151,20 +2311,20 @@
         <v>34808.8524159579</v>
       </c>
       <c r="D16" s="23" t="n">
-        <f aca="false">C16*Input!$B$12</f>
+        <f aca="false">MIN(C16,Input!$B$51)*Input!$B$12</f>
         <v>9074.66782484022</v>
       </c>
       <c r="E16" s="23" t="n">
         <f aca="false">G15</f>
-        <v>137035.823404625</v>
+        <v>122832.524814237</v>
       </c>
       <c r="F16" s="23" t="n">
-        <f aca="false">(E16+D16)*Input!$B$14</f>
-        <v>2922.20982458931</v>
+        <f aca="false">E16*Input!$B$14</f>
+        <v>614.162624071185</v>
       </c>
       <c r="G16" s="23" t="n">
         <f aca="false">IF(B16&lt;Input!$B$6,E16+D16+F16,E16)</f>
-        <v>149032.701054055</v>
+        <v>132521.355263148</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2180,20 +2340,20 @@
         <v>35156.9409401175</v>
       </c>
       <c r="D17" s="23" t="n">
-        <f aca="false">C17*Input!$B$12</f>
+        <f aca="false">MIN(C17,Input!$B$51)*Input!$B$12</f>
         <v>9165.41450308862</v>
       </c>
       <c r="E17" s="23" t="n">
         <f aca="false">G16</f>
-        <v>149032.701054055</v>
+        <v>132521.355263148</v>
       </c>
       <c r="F17" s="23" t="n">
-        <f aca="false">(E17+D17)*Input!$B$14</f>
-        <v>3163.96231114287</v>
+        <f aca="false">E17*Input!$B$14</f>
+        <v>662.606776315742</v>
       </c>
       <c r="G17" s="23" t="n">
         <f aca="false">IF(B17&lt;Input!$B$6,E17+D17+F17,E17)</f>
-        <v>161362.077868286</v>
+        <v>142349.376542553</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2209,20 +2369,20 @@
         <v>35508.5103495186</v>
       </c>
       <c r="D18" s="23" t="n">
-        <f aca="false">C18*Input!$B$12</f>
+        <f aca="false">MIN(C18,Input!$B$51)*Input!$B$12</f>
         <v>9257.06864811951</v>
       </c>
       <c r="E18" s="23" t="n">
         <f aca="false">G17</f>
-        <v>161362.077868286</v>
+        <v>142349.376542553</v>
       </c>
       <c r="F18" s="23" t="n">
-        <f aca="false">(E18+D18)*Input!$B$14</f>
-        <v>3412.38293032812</v>
+        <f aca="false">E18*Input!$B$14</f>
+        <v>711.746882712764</v>
       </c>
       <c r="G18" s="23" t="n">
         <f aca="false">IF(B18&lt;Input!$B$6,E18+D18+F18,E18)</f>
-        <v>174031.529446734</v>
+        <v>152318.192073385</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2238,20 +2398,20 @@
         <v>35863.5954530138</v>
       </c>
       <c r="D19" s="23" t="n">
-        <f aca="false">C19*Input!$B$12</f>
+        <f aca="false">MIN(C19,Input!$B$51)*Input!$B$12</f>
         <v>9349.6393346007</v>
       </c>
       <c r="E19" s="23" t="n">
         <f aca="false">G18</f>
-        <v>174031.529446734</v>
+        <v>152318.192073385</v>
       </c>
       <c r="F19" s="23" t="n">
-        <f aca="false">(E19+D19)*Input!$B$14</f>
-        <v>3667.62337562669</v>
+        <f aca="false">E19*Input!$B$14</f>
+        <v>761.590960366925</v>
       </c>
       <c r="G19" s="23" t="n">
         <f aca="false">IF(B19&lt;Input!$B$6,E19+D19+F19,E19)</f>
-        <v>187048.792156961</v>
+        <v>162429.422368353</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2267,20 +2427,20 @@
         <v>36222.231407544</v>
       </c>
       <c r="D20" s="23" t="n">
-        <f aca="false">C20*Input!$B$12</f>
+        <f aca="false">MIN(C20,Input!$B$51)*Input!$B$12</f>
         <v>9443.13572794671</v>
       </c>
       <c r="E20" s="23" t="n">
         <f aca="false">G19</f>
-        <v>187048.792156961</v>
+        <v>162429.422368353</v>
       </c>
       <c r="F20" s="23" t="n">
-        <f aca="false">(E20+D20)*Input!$B$14</f>
-        <v>3929.83855769816</v>
+        <f aca="false">E20*Input!$B$14</f>
+        <v>812.147111841763</v>
       </c>
       <c r="G20" s="23" t="n">
         <f aca="false">IF(B20&lt;Input!$B$6,E20+D20+F20,E20)</f>
-        <v>200421.766442606</v>
+        <v>172684.705208141</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2296,20 +2456,20 @@
         <v>36584.4537216194</v>
       </c>
       <c r="D21" s="23" t="n">
-        <f aca="false">C21*Input!$B$12</f>
+        <f aca="false">MIN(C21,Input!$B$51)*Input!$B$12</f>
         <v>9537.56708522618</v>
       </c>
       <c r="E21" s="23" t="n">
         <f aca="false">G20</f>
-        <v>200421.766442606</v>
+        <v>172684.705208141</v>
       </c>
       <c r="F21" s="23" t="n">
-        <f aca="false">(E21+D21)*Input!$B$14</f>
-        <v>4199.18667055665</v>
+        <f aca="false">E21*Input!$B$14</f>
+        <v>863.423526040706</v>
       </c>
       <c r="G21" s="23" t="n">
         <f aca="false">IF(B21&lt;Input!$B$6,E21+D21+F21,E21)</f>
-        <v>214158.520198389</v>
+        <v>183085.695819408</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2325,20 +2485,20 @@
         <v>36950.2982588356</v>
       </c>
       <c r="D22" s="23" t="n">
-        <f aca="false">C22*Input!$B$12</f>
+        <f aca="false">MIN(C22,Input!$B$51)*Input!$B$12</f>
         <v>9632.94275607844</v>
       </c>
       <c r="E22" s="23" t="n">
         <f aca="false">G21</f>
-        <v>214158.520198389</v>
+        <v>183085.695819408</v>
       </c>
       <c r="F22" s="23" t="n">
-        <f aca="false">(E22+D22)*Input!$B$14</f>
-        <v>4475.82925908935</v>
+        <f aca="false">E22*Input!$B$14</f>
+        <v>915.42847909704</v>
       </c>
       <c r="G22" s="23" t="n">
         <f aca="false">IF(B22&lt;Input!$B$6,E22+D22+F22,E22)</f>
-        <v>228267.292213557</v>
+        <v>193634.067054584</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2354,20 +2514,20 @@
         <v>37319.801241424</v>
       </c>
       <c r="D23" s="23" t="n">
-        <f aca="false">C23*Input!$B$12</f>
+        <f aca="false">MIN(C23,Input!$B$51)*Input!$B$12</f>
         <v>9729.27218363922</v>
       </c>
       <c r="E23" s="23" t="n">
         <f aca="false">G22</f>
-        <v>228267.292213557</v>
+        <v>193634.067054584</v>
       </c>
       <c r="F23" s="23" t="n">
-        <f aca="false">(E23+D23)*Input!$B$14</f>
-        <v>4759.93128794392</v>
+        <f aca="false">E23*Input!$B$14</f>
+        <v>968.170335272917</v>
       </c>
       <c r="G23" s="23" t="n">
         <f aca="false">IF(B23&lt;Input!$B$6,E23+D23+F23,E23)</f>
-        <v>242756.49568514</v>
+        <v>204331.509573496</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2383,20 +2543,20 @@
         <v>37692.9992538382</v>
       </c>
       <c r="D24" s="23" t="n">
-        <f aca="false">C24*Input!$B$12</f>
+        <f aca="false">MIN(C24,Input!$B$51)*Input!$B$12</f>
         <v>9826.56490547561</v>
       </c>
       <c r="E24" s="23" t="n">
         <f aca="false">G23</f>
-        <v>242756.49568514</v>
+        <v>204331.509573496</v>
       </c>
       <c r="F24" s="23" t="n">
-        <f aca="false">(E24+D24)*Input!$B$14</f>
-        <v>5051.66121181231</v>
+        <f aca="false">E24*Input!$B$14</f>
+        <v>1021.65754786748</v>
       </c>
       <c r="G24" s="23" t="n">
         <f aca="false">IF(B24&lt;Input!$B$6,E24+D24+F24,E24)</f>
-        <v>257634.721802428</v>
+        <v>215179.732026839</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2412,20 +2572,20 @@
         <v>38069.9292463766</v>
       </c>
       <c r="D25" s="23" t="n">
-        <f aca="false">C25*Input!$B$12</f>
+        <f aca="false">MIN(C25,Input!$B$51)*Input!$B$12</f>
         <v>9924.83055453037</v>
       </c>
       <c r="E25" s="23" t="n">
         <f aca="false">G24</f>
-        <v>257634.721802428</v>
+        <v>215179.732026839</v>
       </c>
       <c r="F25" s="23" t="n">
-        <f aca="false">(E25+D25)*Input!$B$14</f>
-        <v>5351.19104713917</v>
+        <f aca="false">E25*Input!$B$14</f>
+        <v>1075.89866013419</v>
       </c>
       <c r="G25" s="23" t="n">
         <f aca="false">IF(B25&lt;Input!$B$6,E25+D25+F25,E25)</f>
-        <v>272910.743404098</v>
+        <v>226180.461241503</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2441,20 +2601,20 @@
         <v>38450.6285388403</v>
       </c>
       <c r="D26" s="23" t="n">
-        <f aca="false">C26*Input!$B$12</f>
+        <f aca="false">MIN(C26,Input!$B$51)*Input!$B$12</f>
         <v>10024.0788600757</v>
       </c>
       <c r="E26" s="23" t="n">
         <f aca="false">G25</f>
-        <v>272910.743404098</v>
+        <v>226180.461241503</v>
       </c>
       <c r="F26" s="23" t="n">
-        <f aca="false">(E26+D26)*Input!$B$14</f>
-        <v>5658.69644528346</v>
+        <f aca="false">E26*Input!$B$14</f>
+        <v>1130.90230620752</v>
       </c>
       <c r="G26" s="23" t="n">
         <f aca="false">IF(B26&lt;Input!$B$6,E26+D26+F26,E26)</f>
-        <v>288593.518709457</v>
+        <v>237335.442407787</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2470,20 +2630,20 @@
         <v>38835.1348242287</v>
       </c>
       <c r="D27" s="23" t="n">
-        <f aca="false">C27*Input!$B$12</f>
+        <f aca="false">MIN(C27,Input!$B$51)*Input!$B$12</f>
         <v>10124.3196486764</v>
       </c>
       <c r="E27" s="23" t="n">
         <f aca="false">G26</f>
-        <v>288593.518709457</v>
+        <v>237335.442407787</v>
       </c>
       <c r="F27" s="23" t="n">
-        <f aca="false">(E27+D27)*Input!$B$14</f>
-        <v>5974.35676716266</v>
+        <f aca="false">E27*Input!$B$14</f>
+        <v>1186.67721203893</v>
       </c>
       <c r="G27" s="23" t="n">
         <f aca="false">IF(B27&lt;Input!$B$6,E27+D27+F27,E27)</f>
-        <v>304692.195125296</v>
+        <v>248646.439268502</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2499,20 +2659,20 @@
         <v>39223.486172471</v>
       </c>
       <c r="D28" s="23" t="n">
-        <f aca="false">C28*Input!$B$12</f>
+        <f aca="false">MIN(C28,Input!$B$51)*Input!$B$12</f>
         <v>10225.5628451632</v>
       </c>
       <c r="E28" s="23" t="n">
         <f aca="false">G27</f>
-        <v>304692.195125296</v>
+        <v>248646.439268502</v>
       </c>
       <c r="F28" s="23" t="n">
-        <f aca="false">(E28+D28)*Input!$B$14</f>
-        <v>6298.35515940918</v>
+        <f aca="false">E28*Input!$B$14</f>
+        <v>1243.23219634251</v>
       </c>
       <c r="G28" s="23" t="n">
         <f aca="false">IF(B28&lt;Input!$B$6,E28+D28+F28,E28)</f>
-        <v>321216.113129868</v>
+        <v>260115.234310008</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2528,20 +2688,20 @@
         <v>39615.7210341957</v>
       </c>
       <c r="D29" s="23" t="n">
-        <f aca="false">C29*Input!$B$12</f>
+        <f aca="false">MIN(C29,Input!$B$51)*Input!$B$12</f>
         <v>10327.8184736148</v>
       </c>
       <c r="E29" s="23" t="n">
         <f aca="false">G28</f>
-        <v>321216.113129868</v>
+        <v>260115.234310008</v>
       </c>
       <c r="F29" s="23" t="n">
-        <f aca="false">(E29+D29)*Input!$B$14</f>
-        <v>6630.87863206966</v>
+        <f aca="false">E29*Input!$B$14</f>
+        <v>1300.57617155004</v>
       </c>
       <c r="G29" s="23" t="n">
         <f aca="false">IF(B29&lt;Input!$B$6,E29+D29+F29,E29)</f>
-        <v>338174.810235553</v>
+        <v>271743.628955172</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2557,20 +2717,20 @@
         <v>40011.8782445377</v>
       </c>
       <c r="D30" s="23" t="n">
-        <f aca="false">C30*Input!$B$12</f>
+        <f aca="false">MIN(C30,Input!$B$51)*Input!$B$12</f>
         <v>10431.096658351</v>
       </c>
       <c r="E30" s="23" t="n">
         <f aca="false">G29</f>
-        <v>338174.810235553</v>
+        <v>271743.628955172</v>
       </c>
       <c r="F30" s="23" t="n">
-        <f aca="false">(E30+D30)*Input!$B$14</f>
-        <v>6972.11813787807</v>
+        <f aca="false">E30*Input!$B$14</f>
+        <v>1358.71814477586</v>
       </c>
       <c r="G30" s="23" t="n">
         <f aca="false">IF(B30&lt;Input!$B$6,E30+D30+F30,E30)</f>
-        <v>355578.025031782</v>
+        <v>283533.443758299</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2586,20 +2746,20 @@
         <v>40411.9970269831</v>
       </c>
       <c r="D31" s="23" t="n">
-        <f aca="false">C31*Input!$B$12</f>
+        <f aca="false">MIN(C31,Input!$B$51)*Input!$B$12</f>
         <v>10535.4076249345</v>
       </c>
       <c r="E31" s="23" t="n">
         <f aca="false">G30</f>
-        <v>355578.025031782</v>
+        <v>283533.443758299</v>
       </c>
       <c r="F31" s="23" t="n">
-        <f aca="false">(E31+D31)*Input!$B$14</f>
-        <v>7322.26865313432</v>
+        <f aca="false">E31*Input!$B$14</f>
+        <v>1417.6672187915</v>
       </c>
       <c r="G31" s="23" t="n">
         <f aca="false">IF(B31&lt;Input!$B$6,E31+D31+F31,E31)</f>
-        <v>373435.701309851</v>
+        <v>295486.518602025</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2615,20 +2775,20 @@
         <v>40816.1169972529</v>
       </c>
       <c r="D32" s="23" t="n">
-        <f aca="false">C32*Input!$B$12</f>
+        <f aca="false">MIN(C32,Input!$B$51)*Input!$B$12</f>
         <v>10640.7617011838</v>
       </c>
       <c r="E32" s="23" t="n">
         <f aca="false">G31</f>
-        <v>373435.701309851</v>
+        <v>295486.518602025</v>
       </c>
       <c r="F32" s="23" t="n">
-        <f aca="false">(E32+D32)*Input!$B$14</f>
-        <v>7681.52926022069</v>
+        <f aca="false">E32*Input!$B$14</f>
+        <v>1477.43259301013</v>
       </c>
       <c r="G32" s="23" t="n">
         <f aca="false">IF(B32&lt;Input!$B$6,E32+D32+F32,E32)</f>
-        <v>391757.992271255</v>
+        <v>307604.712896219</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2644,20 +2804,20 @@
         <v>41224.2781672254</v>
       </c>
       <c r="D33" s="23" t="n">
-        <f aca="false">C33*Input!$B$12</f>
+        <f aca="false">MIN(C33,Input!$B$51)*Input!$B$12</f>
         <v>10747.1693181957</v>
       </c>
       <c r="E33" s="23" t="n">
         <f aca="false">G32</f>
-        <v>391757.992271255</v>
+        <v>307604.712896219</v>
       </c>
       <c r="F33" s="23" t="n">
-        <f aca="false">(E33+D33)*Input!$B$14</f>
-        <v>8050.10323178902</v>
+        <f aca="false">E33*Input!$B$14</f>
+        <v>1538.0235644811</v>
       </c>
       <c r="G33" s="23" t="n">
         <f aca="false">IF(B33&lt;Input!$B$6,E33+D33+F33,E33)</f>
-        <v>410555.26482124</v>
+        <v>319889.905778896</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2673,20 +2833,20 @@
         <v>41636.5209488977</v>
       </c>
       <c r="D34" s="23" t="n">
-        <f aca="false">C34*Input!$B$12</f>
+        <f aca="false">MIN(C34,Input!$B$51)*Input!$B$12</f>
         <v>10854.6410113776</v>
       </c>
       <c r="E34" s="23" t="n">
         <f aca="false">G33</f>
-        <v>410555.26482124</v>
+        <v>319889.905778896</v>
       </c>
       <c r="F34" s="23" t="n">
-        <f aca="false">(E34+D34)*Input!$B$14</f>
-        <v>8428.19811665235</v>
+        <f aca="false">E34*Input!$B$14</f>
+        <v>1599.44952889448</v>
       </c>
       <c r="G34" s="23" t="n">
         <f aca="false">IF(B34&lt;Input!$B$6,E34+D34+F34,E34)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2702,20 +2862,20 @@
         <v>0</v>
       </c>
       <c r="D35" s="23" t="n">
-        <f aca="false">C35*Input!$B$12</f>
+        <f aca="false">MIN(C35,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E35" s="23" t="n">
         <f aca="false">G34</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F35" s="23" t="n">
-        <f aca="false">(E35+D35)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E35*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G35" s="23" t="n">
         <f aca="false">IF(B35&lt;Input!$B$6,E35+D35+F35,E35)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2731,20 +2891,20 @@
         <v>0</v>
       </c>
       <c r="D36" s="23" t="n">
-        <f aca="false">C36*Input!$B$12</f>
+        <f aca="false">MIN(C36,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E36" s="23" t="n">
         <f aca="false">G35</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F36" s="23" t="n">
-        <f aca="false">(E36+D36)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E36*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G36" s="23" t="n">
         <f aca="false">IF(B36&lt;Input!$B$6,E36+D36+F36,E36)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2760,20 +2920,20 @@
         <v>0</v>
       </c>
       <c r="D37" s="23" t="n">
-        <f aca="false">C37*Input!$B$12</f>
+        <f aca="false">MIN(C37,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E37" s="23" t="n">
         <f aca="false">G36</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F37" s="23" t="n">
-        <f aca="false">(E37+D37)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E37*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G37" s="23" t="n">
         <f aca="false">IF(B37&lt;Input!$B$6,E37+D37+F37,E37)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2789,20 +2949,20 @@
         <v>0</v>
       </c>
       <c r="D38" s="23" t="n">
-        <f aca="false">C38*Input!$B$12</f>
+        <f aca="false">MIN(C38,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E38" s="23" t="n">
         <f aca="false">G37</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F38" s="23" t="n">
-        <f aca="false">(E38+D38)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E38*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G38" s="23" t="n">
         <f aca="false">IF(B38&lt;Input!$B$6,E38+D38+F38,E38)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2818,20 +2978,20 @@
         <v>0</v>
       </c>
       <c r="D39" s="23" t="n">
-        <f aca="false">C39*Input!$B$12</f>
+        <f aca="false">MIN(C39,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E39" s="23" t="n">
         <f aca="false">G38</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F39" s="23" t="n">
-        <f aca="false">(E39+D39)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E39*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G39" s="23" t="n">
         <f aca="false">IF(B39&lt;Input!$B$6,E39+D39+F39,E39)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2847,20 +3007,20 @@
         <v>0</v>
       </c>
       <c r="D40" s="23" t="n">
-        <f aca="false">C40*Input!$B$12</f>
+        <f aca="false">MIN(C40,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E40" s="23" t="n">
         <f aca="false">G39</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F40" s="23" t="n">
-        <f aca="false">(E40+D40)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E40*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G40" s="23" t="n">
         <f aca="false">IF(B40&lt;Input!$B$6,E40+D40+F40,E40)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2876,20 +3036,20 @@
         <v>0</v>
       </c>
       <c r="D41" s="23" t="n">
-        <f aca="false">C41*Input!$B$12</f>
+        <f aca="false">MIN(C41,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E41" s="23" t="n">
         <f aca="false">G40</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F41" s="23" t="n">
-        <f aca="false">(E41+D41)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E41*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G41" s="23" t="n">
         <f aca="false">IF(B41&lt;Input!$B$6,E41+D41+F41,E41)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2905,20 +3065,20 @@
         <v>0</v>
       </c>
       <c r="D42" s="23" t="n">
-        <f aca="false">C42*Input!$B$12</f>
+        <f aca="false">MIN(C42,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E42" s="23" t="n">
         <f aca="false">G41</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F42" s="23" t="n">
-        <f aca="false">(E42+D42)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E42*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G42" s="23" t="n">
         <f aca="false">IF(B42&lt;Input!$B$6,E42+D42+F42,E42)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2934,20 +3094,20 @@
         <v>0</v>
       </c>
       <c r="D43" s="23" t="n">
-        <f aca="false">C43*Input!$B$12</f>
+        <f aca="false">MIN(C43,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E43" s="23" t="n">
         <f aca="false">G42</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F43" s="23" t="n">
-        <f aca="false">(E43+D43)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E43*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G43" s="23" t="n">
         <f aca="false">IF(B43&lt;Input!$B$6,E43+D43+F43,E43)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2963,20 +3123,20 @@
         <v>0</v>
       </c>
       <c r="D44" s="23" t="n">
-        <f aca="false">C44*Input!$B$12</f>
+        <f aca="false">MIN(C44,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E44" s="23" t="n">
         <f aca="false">G43</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F44" s="23" t="n">
-        <f aca="false">(E44+D44)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E44*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G44" s="23" t="n">
         <f aca="false">IF(B44&lt;Input!$B$6,E44+D44+F44,E44)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2992,20 +3152,20 @@
         <v>0</v>
       </c>
       <c r="D45" s="23" t="n">
-        <f aca="false">C45*Input!$B$12</f>
+        <f aca="false">MIN(C45,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E45" s="23" t="n">
         <f aca="false">G44</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F45" s="23" t="n">
-        <f aca="false">(E45+D45)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E45*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G45" s="23" t="n">
         <f aca="false">IF(B45&lt;Input!$B$6,E45+D45+F45,E45)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3021,20 +3181,20 @@
         <v>0</v>
       </c>
       <c r="D46" s="23" t="n">
-        <f aca="false">C46*Input!$B$12</f>
+        <f aca="false">MIN(C46,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E46" s="23" t="n">
         <f aca="false">G45</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F46" s="23" t="n">
-        <f aca="false">(E46+D46)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E46*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G46" s="23" t="n">
         <f aca="false">IF(B46&lt;Input!$B$6,E46+D46+F46,E46)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3050,20 +3210,20 @@
         <v>0</v>
       </c>
       <c r="D47" s="23" t="n">
-        <f aca="false">C47*Input!$B$12</f>
+        <f aca="false">MIN(C47,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E47" s="23" t="n">
         <f aca="false">G46</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F47" s="23" t="n">
-        <f aca="false">(E47+D47)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E47*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G47" s="23" t="n">
         <f aca="false">IF(B47&lt;Input!$B$6,E47+D47+F47,E47)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,20 +3239,20 @@
         <v>0</v>
       </c>
       <c r="D48" s="23" t="n">
-        <f aca="false">C48*Input!$B$12</f>
+        <f aca="false">MIN(C48,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E48" s="23" t="n">
         <f aca="false">G47</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F48" s="23" t="n">
-        <f aca="false">(E48+D48)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E48*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G48" s="23" t="n">
         <f aca="false">IF(B48&lt;Input!$B$6,E48+D48+F48,E48)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3108,20 +3268,20 @@
         <v>0</v>
       </c>
       <c r="D49" s="23" t="n">
-        <f aca="false">C49*Input!$B$12</f>
+        <f aca="false">MIN(C49,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E49" s="23" t="n">
         <f aca="false">G48</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F49" s="23" t="n">
-        <f aca="false">(E49+D49)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E49*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G49" s="23" t="n">
         <f aca="false">IF(B49&lt;Input!$B$6,E49+D49+F49,E49)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3137,20 +3297,20 @@
         <v>0</v>
       </c>
       <c r="D50" s="23" t="n">
-        <f aca="false">C50*Input!$B$12</f>
+        <f aca="false">MIN(C50,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E50" s="23" t="n">
         <f aca="false">G49</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F50" s="23" t="n">
-        <f aca="false">(E50+D50)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E50*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G50" s="23" t="n">
         <f aca="false">IF(B50&lt;Input!$B$6,E50+D50+F50,E50)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3166,20 +3326,20 @@
         <v>0</v>
       </c>
       <c r="D51" s="23" t="n">
-        <f aca="false">C51*Input!$B$12</f>
+        <f aca="false">MIN(C51,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E51" s="23" t="n">
         <f aca="false">G50</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F51" s="23" t="n">
-        <f aca="false">(E51+D51)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E51*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G51" s="23" t="n">
         <f aca="false">IF(B51&lt;Input!$B$6,E51+D51+F51,E51)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3195,20 +3355,20 @@
         <v>0</v>
       </c>
       <c r="D52" s="23" t="n">
-        <f aca="false">C52*Input!$B$12</f>
+        <f aca="false">MIN(C52,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E52" s="23" t="n">
         <f aca="false">G51</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F52" s="23" t="n">
-        <f aca="false">(E52+D52)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E52*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G52" s="23" t="n">
         <f aca="false">IF(B52&lt;Input!$B$6,E52+D52+F52,E52)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3224,20 +3384,20 @@
         <v>0</v>
       </c>
       <c r="D53" s="23" t="n">
-        <f aca="false">C53*Input!$B$12</f>
+        <f aca="false">MIN(C53,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E53" s="23" t="n">
         <f aca="false">G52</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F53" s="23" t="n">
-        <f aca="false">(E53+D53)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E53*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G53" s="23" t="n">
         <f aca="false">IF(B53&lt;Input!$B$6,E53+D53+F53,E53)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3253,25 +3413,25 @@
         <v>0</v>
       </c>
       <c r="D54" s="23" t="n">
-        <f aca="false">C54*Input!$B$12</f>
+        <f aca="false">MIN(C54,Input!$B$51)*Input!$B$12</f>
         <v>0</v>
       </c>
       <c r="E54" s="23" t="n">
         <f aca="false">G53</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
       <c r="F54" s="23" t="n">
-        <f aca="false">(E54+D54)*Input!$B$14</f>
-        <v>8596.7620789854</v>
+        <f aca="false">E54*Input!$B$14</f>
+        <v>1661.71998159584</v>
       </c>
       <c r="G54" s="23" t="n">
         <f aca="false">IF(B54&lt;Input!$B$6,E54+D54+F54,E54)</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3282,16 +3442,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="B58" s="25" t="n">
         <f aca="false">INDEX(G5:G54,MATCH(Input!$B$6-1,B5:B54,0))</f>
-        <v>429838.10394927</v>
+        <v>332343.996319168</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="B59" s="26" t="n">
         <f aca="false">Input!$B$43</f>
@@ -3300,25 +3460,25 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B60" s="27" t="n">
         <f aca="false">B58*B59</f>
-        <v>18356.3036684952</v>
+        <v>14192.8025058381</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B61" s="25" t="n">
         <f aca="false">B60/13</f>
-        <v>1412.02335911502</v>
+        <v>1091.75403891063</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B62" s="25" t="n">
         <f aca="false">Input!$B$23*(1+Input!$B$24)^(Input!$B$7-1)</f>
@@ -3327,11 +3487,56 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B63" s="28" t="n">
         <f aca="false">IF(B62&gt;0,B60/B62,0)</f>
-        <v>0.440870256451655</v>
+        <v>0.340873881447914</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B64" s="25" t="n">
+        <f aca="false">IF(B60&lt;=28000,B60*0.23,IF(B60&lt;=50000,6440+(B60-28000)*0.33,13700+(B60-50000)*0.43))</f>
+        <v>3264.34457634277</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B65" s="25" t="n">
+        <f aca="false">IF(B60&lt;=8500,1955,IF(B60&lt;=28000,700+1255*(28000-B60)/19500,IF(B60&lt;=50000,700*(50000-B60)/22000,0)))</f>
+        <v>1588.61706949606</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B66" s="25" t="n">
+        <f aca="false">IF(B64-B65&gt;0,B60*0.02,0)</f>
+        <v>283.856050116763</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B67" s="27" t="n">
+        <f aca="false">B60-MAX(0,B64-B65)-B66</f>
+        <v>12233.2189488747</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B68" s="25" t="n">
+        <f aca="false">B67/13</f>
+        <v>941.016842221128</v>
       </c>
     </row>
   </sheetData>
@@ -3365,7 +3570,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3373,7 +3578,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3381,18 +3586,18 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="B5" s="23" t="n">
         <f aca="false">Input!$B$21</f>
@@ -3416,86 +3621,86 @@
         <v>40000</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B7" s="23" t="n">
         <f aca="false">B6*Input!$B$12</f>
         <v>8133.84</v>
       </c>
       <c r="C7" s="23" t="n">
-        <f aca="false">C6*Input!$B$12</f>
+        <f aca="false">MIN(C6,Input!$B$51)*Input!$B$12</f>
         <v>10428</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B8" s="23" t="n">
-        <f aca="false">MIN(Input!$B$28,5300)*0</f>
+        <f aca="false">MIN(Input!$B$28,Input!$B$48,Input!$B$52)</f>
         <v>0</v>
       </c>
       <c r="C8" s="23" t="n">
-        <f aca="false">MIN(Input!$B$28,5300)</f>
+        <f aca="false">MIN(Input!$B$28,Input!$B$48)</f>
         <v>0</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="B9" s="29" t="n">
-        <f aca="false">MAX(0,B6-B7-B8)</f>
+        <f aca="false">MAX(0,B6-B7)</f>
         <v>23066.16</v>
       </c>
       <c r="C9" s="29" t="n">
-        <f aca="false">MAX(0,C6-C7-C8)</f>
+        <f aca="false">MAX(0,C6-C7+Input!$B$52-C8)</f>
         <v>29572</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="B10" s="23" t="n">
-        <f aca="false">B9*Input!$B$36</f>
+        <f aca="false">B9*Input!$B$36+IF(MAX(0,Input!$B$52-B8)&lt;=28000,MAX(0,Input!$B$52-B8)*0.23,IF(MAX(0,Input!$B$52-B8)&lt;=50000,6440+(MAX(0,Input!$B$52-B8)-28000)*0.33,13700+(MAX(0,Input!$B$52-B8)-50000)*0.43))</f>
         <v>3459.924</v>
       </c>
       <c r="C10" s="23" t="n">
-        <f aca="false">IF(C9&lt;=28000,C9*0.23,IF(C9&lt;=50000,6440+(C9-28000)*0.33,6440+7260+(C9-50000)*0.43))</f>
+        <f aca="false">IF(C9&lt;=28000,C9*0.23,IF(C9&lt;=50000,6440+(C9-28000)*0.33,13700+(C9-50000)*0.43))</f>
         <v>6958.76</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="B11" s="30" t="n">
-        <f aca="false">B6-B7-B10</f>
+        <f aca="false">B6-B7+Input!$B$52-B10</f>
         <v>19606.236</v>
       </c>
       <c r="C11" s="30" t="n">
-        <f aca="false">C6-C7-C10</f>
+        <f aca="false">C6-C7+Input!$B$52-C10</f>
         <v>22613.24</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -3503,20 +3708,20 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="B14" s="23" t="n">
-        <f aca="false">MAX(0,B6-B7)*Input!$B$36</f>
+        <f aca="false">B9*Input!$B$36+IF(Input!$B$52&lt;=28000,Input!$B$52*0.23,IF(Input!$B$52&lt;=50000,6440+(Input!$B$52-28000)*0.33,13700+(Input!$B$52-50000)*0.43))</f>
         <v>3459.924</v>
       </c>
       <c r="C14" s="23" t="n">
-        <f aca="false">IF(MAX(0,C6-C7)&lt;=28000,MAX(0,C6-C7)*0.23,IF(MAX(0,C6-C7)&lt;=50000,6440+(MAX(0,C6-C7)-28000)*0.33,6440+7260+(MAX(0,C6-C7)-50000)*0.43))</f>
+        <f aca="false">IF(MAX(0,C6-C7+Input!$B$52)&lt;=28000,MAX(0,C6-C7+Input!$B$52)*0.23,IF(MAX(0,C6-C7+Input!$B$52)&lt;=50000,6440+(MAX(0,C6-C7+Input!$B$52)-28000)*0.33,13700+(MAX(0,C6-C7+Input!$B$52)-50000)*0.43))</f>
         <v>6958.76</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="B15" s="31" t="n">
         <f aca="false">B14-B10</f>
@@ -3527,12 +3732,12 @@
         <v>0</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B17" s="32"/>
       <c r="C17" s="32"/>
@@ -3540,7 +3745,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="32"/>
@@ -3548,7 +3753,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="32" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="32"/>
@@ -3556,7 +3761,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="32"/>
@@ -3564,7 +3769,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
@@ -3572,7 +3777,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="32"/>
@@ -3580,7 +3785,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="32"/>
@@ -3635,7 +3840,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3645,25 +3850,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5118,7 +5323,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -5128,7 +5333,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B58" s="25" t="n">
         <f aca="false">INDEX(F5:F54,MATCH(Input!$B$6-1,B5:B54,0))</f>
@@ -5137,7 +5342,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B59" s="25" t="n">
         <f aca="false">Input!$B$31+SUMIF(B5:B54,"&lt;"&amp;Input!$B$6,C5:C54)</f>
@@ -5146,7 +5351,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B60" s="25" t="n">
         <f aca="false">(Input!$B$31*(1+Input!$B$39)^(-Input!$B$7)+SUM(G5:G54))*Input!$B$38</f>
@@ -5155,7 +5360,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B61" s="27" t="n">
         <f aca="false">B58-B60</f>
@@ -5164,7 +5369,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B62" s="11" t="n">
         <f aca="false">B61*Input!$B$43</f>
@@ -5173,7 +5378,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="32" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="B64" s="32"/>
       <c r="C64" s="32"/>
@@ -5183,7 +5388,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="32" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="B65" s="32"/>
       <c r="C65" s="32"/>
@@ -5193,7 +5398,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="32" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="B66" s="32"/>
       <c r="C66" s="32"/>
@@ -5203,7 +5408,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="32" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="B67" s="32"/>
       <c r="C67" s="32"/>
@@ -5236,7 +5441,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
@@ -5247,7 +5452,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5255,7 +5460,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5263,7 +5468,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -5275,12 +5480,12 @@
       </c>
       <c r="B5" s="25" t="n">
         <f aca="false">Previdenza!B60</f>
-        <v>18356.3036684952</v>
+        <v>14192.8025058381</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B6" s="25" t="n">
         <f aca="false">Complementare!B62</f>
@@ -5289,25 +5494,34 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>18356.3036684952</v>
+        <v>14192.8025058381</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">B7/13</f>
-        <v>1412.02335911502</v>
+        <v>1091.75403891063</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="27" t="n">
+        <f aca="false">Previdenza!B67+Complementare!B62</f>
+        <v>12233.2189488747</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -5315,7 +5529,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">Previdenza!B62</f>
@@ -5324,46 +5538,46 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">IF(B11&gt;0,B5/B11,0)</f>
-        <v>0.440870256451655</v>
+        <v>0.340873881447914</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B13" s="28" t="n">
         <f aca="false">IF(B11&gt;0,B7/B11,0)</f>
-        <v>0.440870256451655</v>
+        <v>0.340873881447914</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B14" s="27" t="n">
         <f aca="false">MAX(0,B11-B7)</f>
-        <v>23280.2172804025</v>
+        <v>27443.7184430596</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B15" s="25" t="n">
         <f aca="false">B14/13</f>
-        <v>1790.78594464634</v>
+        <v>2111.05526485073</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -5371,49 +5585,49 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="B20" s="23" t="n">
         <f aca="false">B5</f>
-        <v>18356.3036684952</v>
+        <v>14192.8025058381</v>
       </c>
       <c r="C20" s="34" t="n">
         <f aca="false">IF(B11&gt;0,B5/B11,0)</f>
-        <v>0.440870256451655</v>
+        <v>0.340873881447914</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="33" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="B21" s="23" t="n">
         <f aca="false">B7</f>
-        <v>18356.3036684952</v>
+        <v>14192.8025058381</v>
       </c>
       <c r="C21" s="34" t="n">
         <f aca="false">IF(B11&gt;0,B7/B11,0)</f>
-        <v>0.440870256451655</v>
+        <v>0.340873881447914</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="32"/>
@@ -5421,7 +5635,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="32" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="B24" s="32"/>
       <c r="C24" s="32"/>
@@ -5429,7 +5643,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="32" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
@@ -5437,7 +5651,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="32" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
@@ -5445,14 +5659,234 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="32" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="B27" s="32"/>
       <c r="C27" s="32"/>
       <c r="D27" s="32"/>
     </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="34" t="n">
+        <f aca="false">Input!$B$24-0.01</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="34" t="n">
+        <f aca="false">Input!$B$24</f>
+        <v>0.01</v>
+      </c>
+      <c r="D32" s="34" t="n">
+        <f aca="false">Input!$B$24+0.01</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33" s="34" t="n">
+        <f aca="false">Input!$B$14-0.005</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="34" t="n">
+        <f aca="false">Input!$B$14</f>
+        <v>0.005</v>
+      </c>
+      <c r="D33" s="34" t="n">
+        <f aca="false">Input!$B$14+0.005</f>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="34" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="C34" s="34" t="n">
+        <f aca="false">Input!$B$15</f>
+        <v>0.018</v>
+      </c>
+      <c r="D34" s="34" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="B35" s="34" t="n">
+        <f aca="false">Input!$B$29-Input!$B$30-0.01</f>
+        <v>0.01</v>
+      </c>
+      <c r="C35" s="34" t="n">
+        <f aca="false">Input!$B$29-Input!$B$30</f>
+        <v>0.02</v>
+      </c>
+      <c r="D35" s="34" t="n">
+        <f aca="false">Input!$B$29-Input!$B$30+0.01</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="B36" s="23" t="n">
+        <f aca="false">(Input!$B$13*(1+B33)^Input!$B$7+SUMPRODUCT((Previdenza!$A$5:$A$54&lt;Input!$B$7)*((Input!$B$23*(1+B32)^Previdenza!$A$5:$A$54+Input!$B$51-ABS(Input!$B$23*(1+B32)^Previdenza!$A$5:$A$54-Input!$B$51))/2)*Input!$B$12*(1+B33)^(Input!$B$7-1-Previdenza!$A$5:$A$54)))*Input!$B$42*(1-B34)^(Input!$B$7/2)</f>
+        <v>10806.0667563697</v>
+      </c>
+      <c r="C36" s="23" t="n">
+        <f aca="false">(Input!$B$13*(1+C33)^Input!$B$7+SUMPRODUCT((Previdenza!$A$5:$A$54&lt;Input!$B$7)*((Input!$B$23*(1+C32)^Previdenza!$A$5:$A$54+Input!$B$51-ABS(Input!$B$23*(1+C32)^Previdenza!$A$5:$A$54-Input!$B$51))/2)*Input!$B$12*(1+C33)^(Input!$B$7-1-Previdenza!$A$5:$A$54)))*Input!$B$42*(1-C34)^(Input!$B$7/2)</f>
+        <v>14192.8025058381</v>
+      </c>
+      <c r="D36" s="23" t="n">
+        <f aca="false">(Input!$B$13*(1+D33)^Input!$B$7+SUMPRODUCT((Previdenza!$A$5:$A$54&lt;Input!$B$7)*((Input!$B$23*(1+D32)^Previdenza!$A$5:$A$54+Input!$B$51-ABS(Input!$B$23*(1+D32)^Previdenza!$A$5:$A$54-Input!$B$51))/2)*Input!$B$12*(1+D33)^(Input!$B$7-1-Previdenza!$A$5:$A$54)))*Input!$B$42*(1-D34)^(Input!$B$7/2)</f>
+        <v>18360.5950322628</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="B37" s="23" t="n">
+        <f aca="false">B36-MAX(0,IF(B36&lt;=28000,B36*0.23,IF(B36&lt;=50000,6440+(B36-28000)*0.33,13700+(B36-50000)*0.43))-IF(B36&lt;=8500,1955,IF(B36&lt;=28000,700+1255*(28000-B36)/19500,IF(B36&lt;=50000,700*(50000-B36)/22000,0))))-IF(IF(B36&lt;=28000,B36*0.23,IF(B36&lt;=50000,6440+(B36-28000)*0.33,13700+(B36-50000)*0.43))-IF(B36&lt;=8500,1955,IF(B36&lt;=28000,700+1255*(28000-B36)/19500,IF(B36&lt;=50000,700*(50000-B36)/22000,0)))&gt;0,B36*0.02,0)</f>
+        <v>9911.13397603397</v>
+      </c>
+      <c r="C37" s="23" t="n">
+        <f aca="false">C36-MAX(0,IF(C36&lt;=28000,C36*0.23,IF(C36&lt;=50000,6440+(C36-28000)*0.33,13700+(C36-50000)*0.43))-IF(C36&lt;=8500,1955,IF(C36&lt;=28000,700+1255*(28000-C36)/19500,IF(C36&lt;=50000,700*(50000-C36)/22000,0))))-IF(IF(C36&lt;=28000,C36*0.23,IF(C36&lt;=50000,6440+(C36-28000)*0.33,13700+(C36-50000)*0.43))-IF(C36&lt;=8500,1955,IF(C36&lt;=28000,700+1255*(28000-C36)/19500,IF(C36&lt;=50000,700*(50000-C36)/22000,0)))&gt;0,C36*0.02,0)</f>
+        <v>12233.2189488746</v>
+      </c>
+      <c r="D37" s="23" t="n">
+        <f aca="false">D36-MAX(0,IF(D36&lt;=28000,D36*0.23,IF(D36&lt;=50000,6440+(D36-28000)*0.33,13700+(D36-50000)*0.43))-IF(D36&lt;=8500,1955,IF(D36&lt;=28000,700+1255*(28000-D36)/19500,IF(D36&lt;=50000,700*(50000-D36)/22000,0))))-IF(IF(D36&lt;=28000,D36*0.23,IF(D36&lt;=50000,6440+(D36-28000)*0.33,13700+(D36-50000)*0.43))-IF(D36&lt;=8500,1955,IF(D36&lt;=28000,700+1255*(28000-D36)/19500,IF(D36&lt;=50000,700*(50000-D36)/22000,0)))&gt;0,D36*0.02,0)</f>
+        <v>15090.8284913515</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="B38" s="23" t="n">
+        <f aca="false">((Input!$B$31*(1+B35)^Input!$B$7+Input!$B$28*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+B35)^(Input!$B$7-Complementare!$A$5:$A$54)))-((Input!$B$31*(1+Input!$B$39)^(-Input!$B$7)+(Input!$B$46+IF(Input!$B$47=1,0,Input!$B$28-Input!$B$46))*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+Input!$B$39)^(Complementare!$A$5:$A$54-Input!$B$7)))*Input!$B$38))*Input!$B$42*(1-B34)^(Input!$B$7/2)</f>
+        <v>0</v>
+      </c>
+      <c r="C38" s="23" t="n">
+        <f aca="false">((Input!$B$31*(1+C35)^Input!$B$7+Input!$B$28*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+C35)^(Input!$B$7-Complementare!$A$5:$A$54)))-((Input!$B$31*(1+Input!$B$39)^(-Input!$B$7)+(Input!$B$46+IF(Input!$B$47=1,0,Input!$B$28-Input!$B$46))*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+Input!$B$39)^(Complementare!$A$5:$A$54-Input!$B$7)))*Input!$B$38))*Input!$B$42*(1-C34)^(Input!$B$7/2)</f>
+        <v>0</v>
+      </c>
+      <c r="D38" s="23" t="n">
+        <f aca="false">((Input!$B$31*(1+D35)^Input!$B$7+Input!$B$28*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+D35)^(Input!$B$7-Complementare!$A$5:$A$54)))-((Input!$B$31*(1+Input!$B$39)^(-Input!$B$7)+(Input!$B$46+IF(Input!$B$47=1,0,Input!$B$28-Input!$B$46))*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+Input!$B$39)^(Complementare!$A$5:$A$54-Input!$B$7)))*Input!$B$38))*Input!$B$42*(1-D34)^(Input!$B$7/2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="B39" s="30" t="n">
+        <f aca="false">B37+B38</f>
+        <v>9911.13397603397</v>
+      </c>
+      <c r="C39" s="30" t="n">
+        <f aca="false">C37+C38</f>
+        <v>12233.2189488746</v>
+      </c>
+      <c r="D39" s="30" t="n">
+        <f aca="false">D37+D38</f>
+        <v>15090.8284913515</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="B40" s="23" t="n">
+        <f aca="false">Input!$B$55</f>
+        <v>18720</v>
+      </c>
+      <c r="C40" s="23" t="n">
+        <f aca="false">Input!$B$55</f>
+        <v>18720</v>
+      </c>
+      <c r="D40" s="23" t="n">
+        <f aca="false">Input!$B$55</f>
+        <v>18720</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="B41" s="31" t="n">
+        <f aca="false">B40-B39</f>
+        <v>8808.86602396603</v>
+      </c>
+      <c r="C41" s="31" t="n">
+        <f aca="false">C40-C39</f>
+        <v>6486.78105112536</v>
+      </c>
+      <c r="D41" s="31" t="n">
+        <f aca="false">D40-D39</f>
+        <v>3629.17150864852</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="B42" s="34" t="n">
+        <f aca="false">IFERROR(B41/B40,0)</f>
+        <v>0.470559082476818</v>
+      </c>
+      <c r="C42" s="34" t="n">
+        <f aca="false">IFERROR(C41/C40,0)</f>
+        <v>0.346516081790884</v>
+      </c>
+      <c r="D42" s="34" t="n">
+        <f aca="false">IFERROR(D41/D40,0)</f>
+        <v>0.193865999393618</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -5463,6 +5897,8 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A44:D44"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/skills/it-pianificazione-autonomi/assets/proiezione-pensione-autonomi.xlsx
+++ b/skills/it-pianificazione-autonomi/assets/proiezione-pensione-autonomi.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -420,7 +420,7 @@
     <t xml:space="preserve">dell'anno dopo in uscita non sono tassati: il fondo rende per capitalizzazione e uscita esente su quella parte.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tassa finale solo sui versamenti dedotti (e sui non dedotti NON comunicati); rendimenti già tassati esclusi (art. 11 c. 6).</t>
+    <t xml:space="preserve">Tassa finale solo sui versamenti dedotti (e sui non dedotti NON comunicati); rendimenti già tassati esclusi (art. 11 c. 6 D.Lgs. 252/2005; dal 2027 art. 258 c. 4 D.Lgs. 117/2026).</t>
   </si>
   <si>
     <t xml:space="preserve">Riepilogo: pensione attesa e gap</t>
@@ -900,34 +900,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1073,7 +1073,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C48"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
@@ -1506,7 +1506,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
@@ -1764,7 +1764,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G63"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
@@ -3356,7 +3356,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="15"/>
@@ -3440,11 +3440,11 @@
         <v>101</v>
       </c>
       <c r="B8" s="23" t="n">
-        <f aca="false">MIN(Input!$B$28,5300)*0</f>
+        <f aca="false">0*MIN(Input!$B$28,Input!$B$48)</f>
         <v>0</v>
       </c>
       <c r="C8" s="23" t="n">
-        <f aca="false">MIN(Input!$B$28,5300)</f>
+        <f aca="false">MIN(Input!$B$28,Input!$B$48)</f>
         <v>0</v>
       </c>
       <c r="D8" s="7" t="s">
@@ -3615,7 +3615,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G67"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
@@ -5237,7 +5237,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>

--- a/skills/it-pianificazione-autonomi/assets/proiezione-pensione-autonomi.xlsx
+++ b/skills/it-pianificazione-autonomi/assets/proiezione-pensione-autonomi.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="191">
   <si>
     <t xml:space="preserve">Proiezione pensione autonomi — Parametri</t>
   </si>
@@ -66,10 +66,10 @@
     <t xml:space="preserve">informativo; imposta tu l'aliquota sotto</t>
   </si>
   <si>
-    <t xml:space="preserve">Aliquota contributiva (montante)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS 26,07%; cassa: aliquota soggettiva (es. Inarcassa 14,5%, Forense 17%)</t>
+    <t xml:space="preserve">Aliquota contributiva (versata)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GS 26,07% (25% IVS + 0,72% + 0,35% ISCRO), deducibile per intero; cassa: aliquota soggettiva (es. Inarcassa 14,5%, Forense 17%)</t>
   </si>
   <si>
     <t xml:space="preserve">Montante previdenziale già accumulato</t>
@@ -90,6 +90,12 @@
     <t xml:space="preserve">il coefficiente cala ~1,8%/biennio; 0 = congelato</t>
   </si>
   <si>
+    <t xml:space="preserve">Aliquota di computo (montante)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a montante va solo l'IVS: GS 25% (24% se pensionato o già coperto); cassa: aliquota soggettiva</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reddito professionale</t>
   </si>
   <si>
@@ -240,7 +246,7 @@
     <t xml:space="preserve">Altri redditi IRPEF (no cedolare secca)</t>
   </si>
   <si>
-    <t xml:space="preserve">affitti a IRPEF, lavoro dipendente part-time: danno capienza alla deduzione del fondo</t>
+    <t xml:space="preserve">solo redditi senza detrazioni proprie (affitti a IRPEF ordinaria): con lavoro dipendente o occasionale le detrazioni (art. 13 TUIR) riducono il risparmio, fino ad azzerarlo</t>
   </si>
   <si>
     <t xml:space="preserve">Spesa mensile attuale</t>
@@ -303,7 +309,7 @@
     <t xml:space="preserve">Reddito</t>
   </si>
   <si>
-    <t xml:space="preserve">Contributo a montante (fino al massimale)</t>
+    <t xml:space="preserve">Contributo a montante (aliquota di computo, fino al massimale)</t>
   </si>
   <si>
     <t xml:space="preserve">Montante inizio</t>
@@ -405,7 +411,7 @@
     <t xml:space="preserve">Risparmio fiscale dal fondo pensione</t>
   </si>
   <si>
-    <t xml:space="preserve">forf.: IRPEF risparmiata sugli altri redditi; ord.: aliquota × versamento</t>
+    <t xml:space="preserve">forf.: IRPEF lorda risparmiata sugli altri redditi (massimo: con lavoro dipendente può essere zero); ord.: aliquota × versamento</t>
   </si>
   <si>
     <t xml:space="preserve">LETTURA: i contributi previdenziali OBBLIGATORI (Gestione Separata o cassa) si deducono in entrambi</t>
@@ -426,7 +432,7 @@
     <t xml:space="preserve">comunicati al fondo, in uscita non sono tassati; va confrontato con un PAC di ETF (più liquido). L'IRPEF è</t>
   </si>
   <si>
-    <t xml:space="preserve">lorda, ante detrazioni: l'imposta ordinaria reale è un po' più bassa. Confronto indicativo.</t>
+    <t xml:space="preserve">lorda, ante detrazioni: in entrambe le colonne il risparmio è un massimo, e con lavoro dipendente le detrazioni possono annullarlo.</t>
   </si>
   <si>
     <t xml:space="preserve">Accumulo del fondo pensione anno per anno (rendimento netto dell'ISC). La rendita finale si somma alla pensione obbligatoria nel Riepilogo.</t>
@@ -537,7 +543,7 @@
     <t xml:space="preserve">Il tasso di sostituzione degli autonomi è strutturalmente più basso di quello dei dipendenti,</t>
   </si>
   <si>
-    <t xml:space="preserve">perché l'aliquota contributiva è minore (26,07% in Gestione Separata, o l'aliquota soggettiva</t>
+    <t xml:space="preserve">perché l'aliquota di computo è minore (25% in Gestione Separata, o l'aliquota soggettiva</t>
   </si>
   <si>
     <t xml:space="preserve">della cassa, contro il 33% del dipendente). Il fondo pensione complementare serve a colmare il gap,</t>
@@ -1298,333 +1304,344 @@
         <v>20</v>
       </c>
     </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>0.78</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B21" s="10" t="n">
         <v>40000</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B22" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B23" s="11" t="n">
         <f aca="false">IF(Input!$B$19=1,Input!$B$21*Input!$B$20,Input!$B$21-Input!$B$22)</f>
         <v>31200</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>0.01</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B28" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>0.03</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>0.01</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B31" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B32" s="6" t="n">
         <v>5</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B36" s="9" t="n">
         <v>0.15</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B37" s="12" t="n">
         <f aca="false">IF(Input!$B$23&lt;=28000,0.23,IF(Input!$B$23&lt;=50000,0.33,0.43))</f>
         <v>0.33</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B38" s="12" t="n">
         <f aca="false">MAX(0.09,0.15-0.003*MAX(0,Input!$B$32-15))</f>
         <v>0.15</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B39" s="9" t="n">
         <v>0.02</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B42" s="13" t="n">
         <f aca="false">VLOOKUP(Input!$B$6,Coefficienti!A5:C19,3,FALSE())</f>
         <v>0.05608</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B43" s="14" t="n">
         <f aca="false">Input!$B$42*(1-Input!$B$15)^(Input!$B$7/2)</f>
         <v>0.0427051568947495</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B46" s="11" t="n">
         <f aca="false">IF(Input!$B$19=1,MIN(Input!$B$28,Input!$B$48,Input!$B$52),MIN(Input!$B$28,Input!$B$48))</f>
         <v>0</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B48" s="10" t="n">
         <v>5300</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B51" s="10" t="n">
         <v>122295</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B53" s="10" t="n">
         <v>2000</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B54" s="9" t="n">
         <v>0.78</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B55" s="11" t="n">
         <f aca="false">Input!$B$53*12*Input!$B$54</f>
         <v>18720</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1674,27 +1691,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1864,12 +1881,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
@@ -1877,7 +1894,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -1885,7 +1902,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -1893,7 +1910,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -1936,7 +1953,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1947,7 +1964,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1958,25 +1975,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1992,8 +2009,8 @@
         <v>31200</v>
       </c>
       <c r="D5" s="23" t="n">
-        <f aca="false">MIN(C5,Input!$B$51)*Input!$B$12</f>
-        <v>8133.84</v>
+        <f aca="false">MIN(C5,Input!$B$51)*Input!$B$16</f>
+        <v>7800</v>
       </c>
       <c r="E5" s="24" t="n">
         <f aca="false">Input!$B$13</f>
@@ -2005,7 +2022,7 @@
       </c>
       <c r="G5" s="23" t="n">
         <f aca="false">IF(B5&lt;Input!$B$6,E5+D5+F5,E5)</f>
-        <v>33258.84</v>
+        <v>32925</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2021,20 +2038,20 @@
         <v>31512</v>
       </c>
       <c r="D6" s="23" t="n">
-        <f aca="false">MIN(C6,Input!$B$51)*Input!$B$12</f>
-        <v>8215.1784</v>
+        <f aca="false">MIN(C6,Input!$B$51)*Input!$B$16</f>
+        <v>7878</v>
       </c>
       <c r="E6" s="23" t="n">
         <f aca="false">G5</f>
-        <v>33258.84</v>
+        <v>32925</v>
       </c>
       <c r="F6" s="23" t="n">
         <f aca="false">E6*Input!$B$14</f>
-        <v>166.2942</v>
+        <v>164.625</v>
       </c>
       <c r="G6" s="23" t="n">
         <f aca="false">IF(B6&lt;Input!$B$6,E6+D6+F6,E6)</f>
-        <v>41640.3126</v>
+        <v>40967.625</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2050,20 +2067,20 @@
         <v>31827.12</v>
       </c>
       <c r="D7" s="23" t="n">
-        <f aca="false">MIN(C7,Input!$B$51)*Input!$B$12</f>
-        <v>8297.330184</v>
+        <f aca="false">MIN(C7,Input!$B$51)*Input!$B$16</f>
+        <v>7956.78</v>
       </c>
       <c r="E7" s="23" t="n">
         <f aca="false">G6</f>
-        <v>41640.3126</v>
+        <v>40967.625</v>
       </c>
       <c r="F7" s="23" t="n">
         <f aca="false">E7*Input!$B$14</f>
-        <v>208.201563</v>
+        <v>204.838125</v>
       </c>
       <c r="G7" s="23" t="n">
         <f aca="false">IF(B7&lt;Input!$B$6,E7+D7+F7,E7)</f>
-        <v>50145.844347</v>
+        <v>49129.243125</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2079,20 +2096,20 @@
         <v>32145.3912</v>
       </c>
       <c r="D8" s="23" t="n">
-        <f aca="false">MIN(C8,Input!$B$51)*Input!$B$12</f>
-        <v>8380.30348584</v>
+        <f aca="false">MIN(C8,Input!$B$51)*Input!$B$16</f>
+        <v>8036.3478</v>
       </c>
       <c r="E8" s="23" t="n">
         <f aca="false">G7</f>
-        <v>50145.844347</v>
+        <v>49129.243125</v>
       </c>
       <c r="F8" s="23" t="n">
         <f aca="false">E8*Input!$B$14</f>
-        <v>250.729221735</v>
+        <v>245.646215625</v>
       </c>
       <c r="G8" s="23" t="n">
         <f aca="false">IF(B8&lt;Input!$B$6,E8+D8+F8,E8)</f>
-        <v>58776.877054575</v>
+        <v>57411.237140625</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2108,20 +2125,20 @@
         <v>32466.845112</v>
       </c>
       <c r="D9" s="23" t="n">
-        <f aca="false">MIN(C9,Input!$B$51)*Input!$B$12</f>
-        <v>8464.1065206984</v>
+        <f aca="false">MIN(C9,Input!$B$51)*Input!$B$16</f>
+        <v>8116.711278</v>
       </c>
       <c r="E9" s="23" t="n">
         <f aca="false">G8</f>
-        <v>58776.877054575</v>
+        <v>57411.237140625</v>
       </c>
       <c r="F9" s="23" t="n">
         <f aca="false">E9*Input!$B$14</f>
-        <v>293.884385272875</v>
+        <v>287.056185703125</v>
       </c>
       <c r="G9" s="23" t="n">
         <f aca="false">IF(B9&lt;Input!$B$6,E9+D9+F9,E9)</f>
-        <v>67534.8679605463</v>
+        <v>65815.0046043281</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2137,20 +2154,20 @@
         <v>32791.51356312</v>
       </c>
       <c r="D10" s="23" t="n">
-        <f aca="false">MIN(C10,Input!$B$51)*Input!$B$12</f>
-        <v>8548.74758590539</v>
+        <f aca="false">MIN(C10,Input!$B$51)*Input!$B$16</f>
+        <v>8197.87839078</v>
       </c>
       <c r="E10" s="23" t="n">
         <f aca="false">G9</f>
-        <v>67534.8679605463</v>
+        <v>65815.0046043281</v>
       </c>
       <c r="F10" s="23" t="n">
         <f aca="false">E10*Input!$B$14</f>
-        <v>337.674339802731</v>
+        <v>329.075023021641</v>
       </c>
       <c r="G10" s="23" t="n">
         <f aca="false">IF(B10&lt;Input!$B$6,E10+D10+F10,E10)</f>
-        <v>76421.2898862544</v>
+        <v>74341.9580181298</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2166,20 +2183,20 @@
         <v>33119.4286987512</v>
       </c>
       <c r="D11" s="23" t="n">
-        <f aca="false">MIN(C11,Input!$B$51)*Input!$B$12</f>
-        <v>8634.23506176444</v>
+        <f aca="false">MIN(C11,Input!$B$51)*Input!$B$16</f>
+        <v>8279.8571746878</v>
       </c>
       <c r="E11" s="23" t="n">
         <f aca="false">G10</f>
-        <v>76421.2898862544</v>
+        <v>74341.9580181298</v>
       </c>
       <c r="F11" s="23" t="n">
         <f aca="false">E11*Input!$B$14</f>
-        <v>382.106449431272</v>
+        <v>371.709790090649</v>
       </c>
       <c r="G11" s="23" t="n">
         <f aca="false">IF(B11&lt;Input!$B$6,E11+D11+F11,E11)</f>
-        <v>85437.6313974501</v>
+        <v>82993.5249829082</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2195,20 +2212,20 @@
         <v>33450.6229857387</v>
       </c>
       <c r="D12" s="23" t="n">
-        <f aca="false">MIN(C12,Input!$B$51)*Input!$B$12</f>
-        <v>8720.57741238208</v>
+        <f aca="false">MIN(C12,Input!$B$51)*Input!$B$16</f>
+        <v>8362.65574643468</v>
       </c>
       <c r="E12" s="23" t="n">
         <f aca="false">G11</f>
-        <v>85437.6313974501</v>
+        <v>82993.5249829082</v>
       </c>
       <c r="F12" s="23" t="n">
         <f aca="false">E12*Input!$B$14</f>
-        <v>427.18815698725</v>
+        <v>414.967624914541</v>
       </c>
       <c r="G12" s="23" t="n">
         <f aca="false">IF(B12&lt;Input!$B$6,E12+D12+F12,E12)</f>
-        <v>94585.3969668194</v>
+        <v>91771.1483542574</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2224,20 +2241,20 @@
         <v>33785.1292155961</v>
       </c>
       <c r="D13" s="23" t="n">
-        <f aca="false">MIN(C13,Input!$B$51)*Input!$B$12</f>
-        <v>8807.78318650591</v>
+        <f aca="false">MIN(C13,Input!$B$51)*Input!$B$16</f>
+        <v>8446.28230389903</v>
       </c>
       <c r="E13" s="23" t="n">
         <f aca="false">G12</f>
-        <v>94585.3969668194</v>
+        <v>91771.1483542574</v>
       </c>
       <c r="F13" s="23" t="n">
         <f aca="false">E13*Input!$B$14</f>
-        <v>472.926984834097</v>
+        <v>458.855741771287</v>
       </c>
       <c r="G13" s="23" t="n">
         <f aca="false">IF(B13&lt;Input!$B$6,E13+D13+F13,E13)</f>
-        <v>103866.107138159</v>
+        <v>100676.286399928</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2253,20 +2270,20 @@
         <v>34122.9805077521</v>
       </c>
       <c r="D14" s="23" t="n">
-        <f aca="false">MIN(C14,Input!$B$51)*Input!$B$12</f>
-        <v>8895.86101837096</v>
+        <f aca="false">MIN(C14,Input!$B$51)*Input!$B$16</f>
+        <v>8530.74512693801</v>
       </c>
       <c r="E14" s="23" t="n">
         <f aca="false">G13</f>
-        <v>103866.107138159</v>
+        <v>100676.286399928</v>
       </c>
       <c r="F14" s="23" t="n">
         <f aca="false">E14*Input!$B$14</f>
-        <v>519.330535690797</v>
+        <v>503.381431999639</v>
       </c>
       <c r="G14" s="23" t="n">
         <f aca="false">IF(B14&lt;Input!$B$6,E14+D14+F14,E14)</f>
-        <v>113281.298692221</v>
+        <v>109710.412958865</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2282,20 +2299,20 @@
         <v>34464.2103128296</v>
       </c>
       <c r="D15" s="23" t="n">
-        <f aca="false">MIN(C15,Input!$B$51)*Input!$B$12</f>
-        <v>8984.81962855467</v>
+        <f aca="false">MIN(C15,Input!$B$51)*Input!$B$16</f>
+        <v>8616.0525782074</v>
       </c>
       <c r="E15" s="23" t="n">
         <f aca="false">G14</f>
-        <v>113281.298692221</v>
+        <v>109710.412958865</v>
       </c>
       <c r="F15" s="23" t="n">
         <f aca="false">E15*Input!$B$14</f>
-        <v>566.406493461106</v>
+        <v>548.552064794327</v>
       </c>
       <c r="G15" s="23" t="n">
         <f aca="false">IF(B15&lt;Input!$B$6,E15+D15+F15,E15)</f>
-        <v>122832.524814237</v>
+        <v>118875.017601867</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2311,20 +2328,20 @@
         <v>34808.8524159579</v>
       </c>
       <c r="D16" s="23" t="n">
-        <f aca="false">MIN(C16,Input!$B$51)*Input!$B$12</f>
-        <v>9074.66782484022</v>
+        <f aca="false">MIN(C16,Input!$B$51)*Input!$B$16</f>
+        <v>8702.21310398947</v>
       </c>
       <c r="E16" s="23" t="n">
         <f aca="false">G15</f>
-        <v>122832.524814237</v>
+        <v>118875.017601867</v>
       </c>
       <c r="F16" s="23" t="n">
         <f aca="false">E16*Input!$B$14</f>
-        <v>614.162624071185</v>
+        <v>594.375088009336</v>
       </c>
       <c r="G16" s="23" t="n">
         <f aca="false">IF(B16&lt;Input!$B$6,E16+D16+F16,E16)</f>
-        <v>132521.355263148</v>
+        <v>128171.605793866</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2340,20 +2357,20 @@
         <v>35156.9409401175</v>
       </c>
       <c r="D17" s="23" t="n">
-        <f aca="false">MIN(C17,Input!$B$51)*Input!$B$12</f>
-        <v>9165.41450308862</v>
+        <f aca="false">MIN(C17,Input!$B$51)*Input!$B$16</f>
+        <v>8789.23523502936</v>
       </c>
       <c r="E17" s="23" t="n">
         <f aca="false">G16</f>
-        <v>132521.355263148</v>
+        <v>128171.605793866</v>
       </c>
       <c r="F17" s="23" t="n">
         <f aca="false">E17*Input!$B$14</f>
-        <v>662.606776315742</v>
+        <v>640.85802896933</v>
       </c>
       <c r="G17" s="23" t="n">
         <f aca="false">IF(B17&lt;Input!$B$6,E17+D17+F17,E17)</f>
-        <v>142349.376542553</v>
+        <v>137601.699057865</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2369,20 +2386,20 @@
         <v>35508.5103495186</v>
       </c>
       <c r="D18" s="23" t="n">
-        <f aca="false">MIN(C18,Input!$B$51)*Input!$B$12</f>
-        <v>9257.06864811951</v>
+        <f aca="false">MIN(C18,Input!$B$51)*Input!$B$16</f>
+        <v>8877.12758737966</v>
       </c>
       <c r="E18" s="23" t="n">
         <f aca="false">G17</f>
-        <v>142349.376542553</v>
+        <v>137601.699057865</v>
       </c>
       <c r="F18" s="23" t="n">
         <f aca="false">E18*Input!$B$14</f>
-        <v>711.746882712764</v>
+        <v>688.008495289323</v>
       </c>
       <c r="G18" s="23" t="n">
         <f aca="false">IF(B18&lt;Input!$B$6,E18+D18+F18,E18)</f>
-        <v>152318.192073385</v>
+        <v>147166.835140534</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2398,20 +2415,20 @@
         <v>35863.5954530138</v>
       </c>
       <c r="D19" s="23" t="n">
-        <f aca="false">MIN(C19,Input!$B$51)*Input!$B$12</f>
-        <v>9349.6393346007</v>
+        <f aca="false">MIN(C19,Input!$B$51)*Input!$B$16</f>
+        <v>8965.89886325346</v>
       </c>
       <c r="E19" s="23" t="n">
         <f aca="false">G18</f>
-        <v>152318.192073385</v>
+        <v>147166.835140534</v>
       </c>
       <c r="F19" s="23" t="n">
         <f aca="false">E19*Input!$B$14</f>
-        <v>761.590960366925</v>
+        <v>735.834175702668</v>
       </c>
       <c r="G19" s="23" t="n">
         <f aca="false">IF(B19&lt;Input!$B$6,E19+D19+F19,E19)</f>
-        <v>162429.422368353</v>
+        <v>156868.56817949</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2427,20 +2444,20 @@
         <v>36222.231407544</v>
       </c>
       <c r="D20" s="23" t="n">
-        <f aca="false">MIN(C20,Input!$B$51)*Input!$B$12</f>
-        <v>9443.13572794671</v>
+        <f aca="false">MIN(C20,Input!$B$51)*Input!$B$16</f>
+        <v>9055.55785188599</v>
       </c>
       <c r="E20" s="23" t="n">
         <f aca="false">G19</f>
-        <v>162429.422368353</v>
+        <v>156868.56817949</v>
       </c>
       <c r="F20" s="23" t="n">
         <f aca="false">E20*Input!$B$14</f>
-        <v>812.147111841763</v>
+        <v>784.342840897449</v>
       </c>
       <c r="G20" s="23" t="n">
         <f aca="false">IF(B20&lt;Input!$B$6,E20+D20+F20,E20)</f>
-        <v>172684.705208141</v>
+        <v>166708.468872273</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2456,20 +2473,20 @@
         <v>36584.4537216194</v>
       </c>
       <c r="D21" s="23" t="n">
-        <f aca="false">MIN(C21,Input!$B$51)*Input!$B$12</f>
-        <v>9537.56708522618</v>
+        <f aca="false">MIN(C21,Input!$B$51)*Input!$B$16</f>
+        <v>9146.11343040485</v>
       </c>
       <c r="E21" s="23" t="n">
         <f aca="false">G20</f>
-        <v>172684.705208141</v>
+        <v>166708.468872273</v>
       </c>
       <c r="F21" s="23" t="n">
         <f aca="false">E21*Input!$B$14</f>
-        <v>863.423526040706</v>
+        <v>833.542344361366</v>
       </c>
       <c r="G21" s="23" t="n">
         <f aca="false">IF(B21&lt;Input!$B$6,E21+D21+F21,E21)</f>
-        <v>183085.695819408</v>
+        <v>176688.124647039</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2485,20 +2502,20 @@
         <v>36950.2982588356</v>
       </c>
       <c r="D22" s="23" t="n">
-        <f aca="false">MIN(C22,Input!$B$51)*Input!$B$12</f>
-        <v>9632.94275607844</v>
+        <f aca="false">MIN(C22,Input!$B$51)*Input!$B$16</f>
+        <v>9237.5745647089</v>
       </c>
       <c r="E22" s="23" t="n">
         <f aca="false">G21</f>
-        <v>183085.695819408</v>
+        <v>176688.124647039</v>
       </c>
       <c r="F22" s="23" t="n">
         <f aca="false">E22*Input!$B$14</f>
-        <v>915.42847909704</v>
+        <v>883.440623235197</v>
       </c>
       <c r="G22" s="23" t="n">
         <f aca="false">IF(B22&lt;Input!$B$6,E22+D22+F22,E22)</f>
-        <v>193634.067054584</v>
+        <v>186809.139834984</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2514,20 +2531,20 @@
         <v>37319.801241424</v>
       </c>
       <c r="D23" s="23" t="n">
-        <f aca="false">MIN(C23,Input!$B$51)*Input!$B$12</f>
-        <v>9729.27218363922</v>
+        <f aca="false">MIN(C23,Input!$B$51)*Input!$B$16</f>
+        <v>9329.95031035599</v>
       </c>
       <c r="E23" s="23" t="n">
         <f aca="false">G22</f>
-        <v>193634.067054584</v>
+        <v>186809.139834984</v>
       </c>
       <c r="F23" s="23" t="n">
         <f aca="false">E23*Input!$B$14</f>
-        <v>968.170335272917</v>
+        <v>934.045699174918</v>
       </c>
       <c r="G23" s="23" t="n">
         <f aca="false">IF(B23&lt;Input!$B$6,E23+D23+F23,E23)</f>
-        <v>204331.509573496</v>
+        <v>197073.135844514</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2543,20 +2560,20 @@
         <v>37692.9992538382</v>
       </c>
       <c r="D24" s="23" t="n">
-        <f aca="false">MIN(C24,Input!$B$51)*Input!$B$12</f>
-        <v>9826.56490547561</v>
+        <f aca="false">MIN(C24,Input!$B$51)*Input!$B$16</f>
+        <v>9423.24981345955</v>
       </c>
       <c r="E24" s="23" t="n">
         <f aca="false">G23</f>
-        <v>204331.509573496</v>
+        <v>197073.135844514</v>
       </c>
       <c r="F24" s="23" t="n">
         <f aca="false">E24*Input!$B$14</f>
-        <v>1021.65754786748</v>
+        <v>985.365679222572</v>
       </c>
       <c r="G24" s="23" t="n">
         <f aca="false">IF(B24&lt;Input!$B$6,E24+D24+F24,E24)</f>
-        <v>215179.732026839</v>
+        <v>207481.751337197</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2572,20 +2589,20 @@
         <v>38069.9292463766</v>
       </c>
       <c r="D25" s="23" t="n">
-        <f aca="false">MIN(C25,Input!$B$51)*Input!$B$12</f>
-        <v>9924.83055453037</v>
+        <f aca="false">MIN(C25,Input!$B$51)*Input!$B$16</f>
+        <v>9517.48231159414</v>
       </c>
       <c r="E25" s="23" t="n">
         <f aca="false">G24</f>
-        <v>215179.732026839</v>
+        <v>207481.751337197</v>
       </c>
       <c r="F25" s="23" t="n">
         <f aca="false">E25*Input!$B$14</f>
-        <v>1075.89866013419</v>
+        <v>1037.40875668598</v>
       </c>
       <c r="G25" s="23" t="n">
         <f aca="false">IF(B25&lt;Input!$B$6,E25+D25+F25,E25)</f>
-        <v>226180.461241503</v>
+        <v>218036.642405477</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2601,20 +2618,20 @@
         <v>38450.6285388403</v>
       </c>
       <c r="D26" s="23" t="n">
-        <f aca="false">MIN(C26,Input!$B$51)*Input!$B$12</f>
-        <v>10024.0788600757</v>
+        <f aca="false">MIN(C26,Input!$B$51)*Input!$B$16</f>
+        <v>9612.65713471009</v>
       </c>
       <c r="E26" s="23" t="n">
         <f aca="false">G25</f>
-        <v>226180.461241503</v>
+        <v>218036.642405477</v>
       </c>
       <c r="F26" s="23" t="n">
         <f aca="false">E26*Input!$B$14</f>
-        <v>1130.90230620752</v>
+        <v>1090.18321202738</v>
       </c>
       <c r="G26" s="23" t="n">
         <f aca="false">IF(B26&lt;Input!$B$6,E26+D26+F26,E26)</f>
-        <v>237335.442407787</v>
+        <v>228739.482752214</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2630,20 +2647,20 @@
         <v>38835.1348242287</v>
       </c>
       <c r="D27" s="23" t="n">
-        <f aca="false">MIN(C27,Input!$B$51)*Input!$B$12</f>
-        <v>10124.3196486764</v>
+        <f aca="false">MIN(C27,Input!$B$51)*Input!$B$16</f>
+        <v>9708.78370605719</v>
       </c>
       <c r="E27" s="23" t="n">
         <f aca="false">G26</f>
-        <v>237335.442407787</v>
+        <v>228739.482752214</v>
       </c>
       <c r="F27" s="23" t="n">
         <f aca="false">E27*Input!$B$14</f>
-        <v>1186.67721203893</v>
+        <v>1143.69741376107</v>
       </c>
       <c r="G27" s="23" t="n">
         <f aca="false">IF(B27&lt;Input!$B$6,E27+D27+F27,E27)</f>
-        <v>248646.439268502</v>
+        <v>239591.963872032</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2659,20 +2676,20 @@
         <v>39223.486172471</v>
       </c>
       <c r="D28" s="23" t="n">
-        <f aca="false">MIN(C28,Input!$B$51)*Input!$B$12</f>
-        <v>10225.5628451632</v>
+        <f aca="false">MIN(C28,Input!$B$51)*Input!$B$16</f>
+        <v>9805.87154311776</v>
       </c>
       <c r="E28" s="23" t="n">
         <f aca="false">G27</f>
-        <v>248646.439268502</v>
+        <v>239591.963872032</v>
       </c>
       <c r="F28" s="23" t="n">
         <f aca="false">E28*Input!$B$14</f>
-        <v>1243.23219634251</v>
+        <v>1197.95981936016</v>
       </c>
       <c r="G28" s="23" t="n">
         <f aca="false">IF(B28&lt;Input!$B$6,E28+D28+F28,E28)</f>
-        <v>260115.234310008</v>
+        <v>250595.79523451</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2688,20 +2705,20 @@
         <v>39615.7210341957</v>
       </c>
       <c r="D29" s="23" t="n">
-        <f aca="false">MIN(C29,Input!$B$51)*Input!$B$12</f>
-        <v>10327.8184736148</v>
+        <f aca="false">MIN(C29,Input!$B$51)*Input!$B$16</f>
+        <v>9903.93025854894</v>
       </c>
       <c r="E29" s="23" t="n">
         <f aca="false">G28</f>
-        <v>260115.234310008</v>
+        <v>250595.79523451</v>
       </c>
       <c r="F29" s="23" t="n">
         <f aca="false">E29*Input!$B$14</f>
-        <v>1300.57617155004</v>
+        <v>1252.97897617255</v>
       </c>
       <c r="G29" s="23" t="n">
         <f aca="false">IF(B29&lt;Input!$B$6,E29+D29+F29,E29)</f>
-        <v>271743.628955172</v>
+        <v>261752.704469232</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2717,20 +2734,20 @@
         <v>40011.8782445377</v>
       </c>
       <c r="D30" s="23" t="n">
-        <f aca="false">MIN(C30,Input!$B$51)*Input!$B$12</f>
-        <v>10431.096658351</v>
+        <f aca="false">MIN(C30,Input!$B$51)*Input!$B$16</f>
+        <v>10002.9695611344</v>
       </c>
       <c r="E30" s="23" t="n">
         <f aca="false">G29</f>
-        <v>271743.628955172</v>
+        <v>261752.704469232</v>
       </c>
       <c r="F30" s="23" t="n">
         <f aca="false">E30*Input!$B$14</f>
-        <v>1358.71814477586</v>
+        <v>1308.76352234616</v>
       </c>
       <c r="G30" s="23" t="n">
         <f aca="false">IF(B30&lt;Input!$B$6,E30+D30+F30,E30)</f>
-        <v>283533.443758299</v>
+        <v>273064.437552712</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2746,20 +2763,20 @@
         <v>40411.9970269831</v>
       </c>
       <c r="D31" s="23" t="n">
-        <f aca="false">MIN(C31,Input!$B$51)*Input!$B$12</f>
-        <v>10535.4076249345</v>
+        <f aca="false">MIN(C31,Input!$B$51)*Input!$B$16</f>
+        <v>10102.9992567458</v>
       </c>
       <c r="E31" s="23" t="n">
         <f aca="false">G30</f>
-        <v>283533.443758299</v>
+        <v>273064.437552712</v>
       </c>
       <c r="F31" s="23" t="n">
         <f aca="false">E31*Input!$B$14</f>
-        <v>1417.6672187915</v>
+        <v>1365.32218776356</v>
       </c>
       <c r="G31" s="23" t="n">
         <f aca="false">IF(B31&lt;Input!$B$6,E31+D31+F31,E31)</f>
-        <v>295486.518602025</v>
+        <v>284532.758997222</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2775,20 +2792,20 @@
         <v>40816.1169972529</v>
       </c>
       <c r="D32" s="23" t="n">
-        <f aca="false">MIN(C32,Input!$B$51)*Input!$B$12</f>
-        <v>10640.7617011838</v>
+        <f aca="false">MIN(C32,Input!$B$51)*Input!$B$16</f>
+        <v>10204.0292493132</v>
       </c>
       <c r="E32" s="23" t="n">
         <f aca="false">G31</f>
-        <v>295486.518602025</v>
+        <v>284532.758997222</v>
       </c>
       <c r="F32" s="23" t="n">
         <f aca="false">E32*Input!$B$14</f>
-        <v>1477.43259301013</v>
+        <v>1422.66379498611</v>
       </c>
       <c r="G32" s="23" t="n">
         <f aca="false">IF(B32&lt;Input!$B$6,E32+D32+F32,E32)</f>
-        <v>307604.712896219</v>
+        <v>296159.452041521</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2804,20 +2821,20 @@
         <v>41224.2781672254</v>
       </c>
       <c r="D33" s="23" t="n">
-        <f aca="false">MIN(C33,Input!$B$51)*Input!$B$12</f>
-        <v>10747.1693181957</v>
+        <f aca="false">MIN(C33,Input!$B$51)*Input!$B$16</f>
+        <v>10306.0695418064</v>
       </c>
       <c r="E33" s="23" t="n">
         <f aca="false">G32</f>
-        <v>307604.712896219</v>
+        <v>296159.452041521</v>
       </c>
       <c r="F33" s="23" t="n">
         <f aca="false">E33*Input!$B$14</f>
-        <v>1538.0235644811</v>
+        <v>1480.79726020761</v>
       </c>
       <c r="G33" s="23" t="n">
         <f aca="false">IF(B33&lt;Input!$B$6,E33+D33+F33,E33)</f>
-        <v>319889.905778896</v>
+        <v>307946.318843535</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2833,20 +2850,20 @@
         <v>41636.5209488977</v>
       </c>
       <c r="D34" s="23" t="n">
-        <f aca="false">MIN(C34,Input!$B$51)*Input!$B$12</f>
-        <v>10854.6410113776</v>
+        <f aca="false">MIN(C34,Input!$B$51)*Input!$B$16</f>
+        <v>10409.1302372244</v>
       </c>
       <c r="E34" s="23" t="n">
         <f aca="false">G33</f>
-        <v>319889.905778896</v>
+        <v>307946.318843535</v>
       </c>
       <c r="F34" s="23" t="n">
         <f aca="false">E34*Input!$B$14</f>
-        <v>1599.44952889448</v>
+        <v>1539.73159421768</v>
       </c>
       <c r="G34" s="23" t="n">
         <f aca="false">IF(B34&lt;Input!$B$6,E34+D34+F34,E34)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2862,20 +2879,20 @@
         <v>0</v>
       </c>
       <c r="D35" s="23" t="n">
-        <f aca="false">MIN(C35,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C35,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E35" s="23" t="n">
         <f aca="false">G34</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F35" s="23" t="n">
         <f aca="false">E35*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G35" s="23" t="n">
         <f aca="false">IF(B35&lt;Input!$B$6,E35+D35+F35,E35)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2891,20 +2908,20 @@
         <v>0</v>
       </c>
       <c r="D36" s="23" t="n">
-        <f aca="false">MIN(C36,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C36,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E36" s="23" t="n">
         <f aca="false">G35</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F36" s="23" t="n">
         <f aca="false">E36*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G36" s="23" t="n">
         <f aca="false">IF(B36&lt;Input!$B$6,E36+D36+F36,E36)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2920,20 +2937,20 @@
         <v>0</v>
       </c>
       <c r="D37" s="23" t="n">
-        <f aca="false">MIN(C37,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C37,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E37" s="23" t="n">
         <f aca="false">G36</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F37" s="23" t="n">
         <f aca="false">E37*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G37" s="23" t="n">
         <f aca="false">IF(B37&lt;Input!$B$6,E37+D37+F37,E37)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2949,20 +2966,20 @@
         <v>0</v>
       </c>
       <c r="D38" s="23" t="n">
-        <f aca="false">MIN(C38,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C38,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E38" s="23" t="n">
         <f aca="false">G37</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F38" s="23" t="n">
         <f aca="false">E38*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G38" s="23" t="n">
         <f aca="false">IF(B38&lt;Input!$B$6,E38+D38+F38,E38)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2978,20 +2995,20 @@
         <v>0</v>
       </c>
       <c r="D39" s="23" t="n">
-        <f aca="false">MIN(C39,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C39,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E39" s="23" t="n">
         <f aca="false">G38</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F39" s="23" t="n">
         <f aca="false">E39*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G39" s="23" t="n">
         <f aca="false">IF(B39&lt;Input!$B$6,E39+D39+F39,E39)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3007,20 +3024,20 @@
         <v>0</v>
       </c>
       <c r="D40" s="23" t="n">
-        <f aca="false">MIN(C40,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C40,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E40" s="23" t="n">
         <f aca="false">G39</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F40" s="23" t="n">
         <f aca="false">E40*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G40" s="23" t="n">
         <f aca="false">IF(B40&lt;Input!$B$6,E40+D40+F40,E40)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3036,20 +3053,20 @@
         <v>0</v>
       </c>
       <c r="D41" s="23" t="n">
-        <f aca="false">MIN(C41,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C41,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E41" s="23" t="n">
         <f aca="false">G40</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F41" s="23" t="n">
         <f aca="false">E41*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G41" s="23" t="n">
         <f aca="false">IF(B41&lt;Input!$B$6,E41+D41+F41,E41)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3065,20 +3082,20 @@
         <v>0</v>
       </c>
       <c r="D42" s="23" t="n">
-        <f aca="false">MIN(C42,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C42,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E42" s="23" t="n">
         <f aca="false">G41</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F42" s="23" t="n">
         <f aca="false">E42*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G42" s="23" t="n">
         <f aca="false">IF(B42&lt;Input!$B$6,E42+D42+F42,E42)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3094,20 +3111,20 @@
         <v>0</v>
       </c>
       <c r="D43" s="23" t="n">
-        <f aca="false">MIN(C43,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C43,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E43" s="23" t="n">
         <f aca="false">G42</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F43" s="23" t="n">
         <f aca="false">E43*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G43" s="23" t="n">
         <f aca="false">IF(B43&lt;Input!$B$6,E43+D43+F43,E43)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3123,20 +3140,20 @@
         <v>0</v>
       </c>
       <c r="D44" s="23" t="n">
-        <f aca="false">MIN(C44,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C44,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E44" s="23" t="n">
         <f aca="false">G43</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F44" s="23" t="n">
         <f aca="false">E44*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G44" s="23" t="n">
         <f aca="false">IF(B44&lt;Input!$B$6,E44+D44+F44,E44)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3152,20 +3169,20 @@
         <v>0</v>
       </c>
       <c r="D45" s="23" t="n">
-        <f aca="false">MIN(C45,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C45,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E45" s="23" t="n">
         <f aca="false">G44</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F45" s="23" t="n">
         <f aca="false">E45*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G45" s="23" t="n">
         <f aca="false">IF(B45&lt;Input!$B$6,E45+D45+F45,E45)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3181,20 +3198,20 @@
         <v>0</v>
       </c>
       <c r="D46" s="23" t="n">
-        <f aca="false">MIN(C46,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C46,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E46" s="23" t="n">
         <f aca="false">G45</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F46" s="23" t="n">
         <f aca="false">E46*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G46" s="23" t="n">
         <f aca="false">IF(B46&lt;Input!$B$6,E46+D46+F46,E46)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3210,20 +3227,20 @@
         <v>0</v>
       </c>
       <c r="D47" s="23" t="n">
-        <f aca="false">MIN(C47,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C47,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E47" s="23" t="n">
         <f aca="false">G46</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F47" s="23" t="n">
         <f aca="false">E47*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G47" s="23" t="n">
         <f aca="false">IF(B47&lt;Input!$B$6,E47+D47+F47,E47)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3239,20 +3256,20 @@
         <v>0</v>
       </c>
       <c r="D48" s="23" t="n">
-        <f aca="false">MIN(C48,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C48,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E48" s="23" t="n">
         <f aca="false">G47</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F48" s="23" t="n">
         <f aca="false">E48*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G48" s="23" t="n">
         <f aca="false">IF(B48&lt;Input!$B$6,E48+D48+F48,E48)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3268,20 +3285,20 @@
         <v>0</v>
       </c>
       <c r="D49" s="23" t="n">
-        <f aca="false">MIN(C49,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C49,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E49" s="23" t="n">
         <f aca="false">G48</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F49" s="23" t="n">
         <f aca="false">E49*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G49" s="23" t="n">
         <f aca="false">IF(B49&lt;Input!$B$6,E49+D49+F49,E49)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3297,20 +3314,20 @@
         <v>0</v>
       </c>
       <c r="D50" s="23" t="n">
-        <f aca="false">MIN(C50,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C50,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E50" s="23" t="n">
         <f aca="false">G49</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F50" s="23" t="n">
         <f aca="false">E50*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G50" s="23" t="n">
         <f aca="false">IF(B50&lt;Input!$B$6,E50+D50+F50,E50)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3326,20 +3343,20 @@
         <v>0</v>
       </c>
       <c r="D51" s="23" t="n">
-        <f aca="false">MIN(C51,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C51,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E51" s="23" t="n">
         <f aca="false">G50</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F51" s="23" t="n">
         <f aca="false">E51*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G51" s="23" t="n">
         <f aca="false">IF(B51&lt;Input!$B$6,E51+D51+F51,E51)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3355,20 +3372,20 @@
         <v>0</v>
       </c>
       <c r="D52" s="23" t="n">
-        <f aca="false">MIN(C52,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C52,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E52" s="23" t="n">
         <f aca="false">G51</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F52" s="23" t="n">
         <f aca="false">E52*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G52" s="23" t="n">
         <f aca="false">IF(B52&lt;Input!$B$6,E52+D52+F52,E52)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3384,20 +3401,20 @@
         <v>0</v>
       </c>
       <c r="D53" s="23" t="n">
-        <f aca="false">MIN(C53,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C53,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E53" s="23" t="n">
         <f aca="false">G52</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F53" s="23" t="n">
         <f aca="false">E53*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G53" s="23" t="n">
         <f aca="false">IF(B53&lt;Input!$B$6,E53+D53+F53,E53)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3413,25 +3430,25 @@
         <v>0</v>
       </c>
       <c r="D54" s="23" t="n">
-        <f aca="false">MIN(C54,Input!$B$51)*Input!$B$12</f>
+        <f aca="false">MIN(C54,Input!$B$51)*Input!$B$16</f>
         <v>0</v>
       </c>
       <c r="E54" s="23" t="n">
         <f aca="false">G53</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
       <c r="F54" s="23" t="n">
         <f aca="false">E54*Input!$B$14</f>
-        <v>1661.71998159584</v>
+        <v>1599.47590337489</v>
       </c>
       <c r="G54" s="23" t="n">
         <f aca="false">IF(B54&lt;Input!$B$6,E54+D54+F54,E54)</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3442,16 +3459,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B58" s="25" t="n">
         <f aca="false">INDEX(G5:G54,MATCH(Input!$B$6-1,B5:B54,0))</f>
-        <v>332343.996319168</v>
+        <v>319895.180674977</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B59" s="26" t="n">
         <f aca="false">Input!$B$43</f>
@@ -3460,25 +3477,25 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B60" s="27" t="n">
         <f aca="false">B58*B59</f>
-        <v>14192.8025058381</v>
+        <v>13661.1738805992</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B61" s="25" t="n">
         <f aca="false">B60/13</f>
-        <v>1091.75403891063</v>
+        <v>1050.85952927686</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B62" s="25" t="n">
         <f aca="false">Input!$B$23*(1+Input!$B$24)^(Input!$B$7-1)</f>
@@ -3487,56 +3504,56 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B63" s="28" t="n">
         <f aca="false">IF(B62&gt;0,B60/B62,0)</f>
-        <v>0.340873881447914</v>
+        <v>0.32810555659456</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B64" s="25" t="n">
         <f aca="false">IF(B60&lt;=28000,B60*0.23,IF(B60&lt;=50000,6440+(B60-28000)*0.33,13700+(B60-50000)*0.43))</f>
-        <v>3264.34457634277</v>
+        <v>3142.0699925378</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B65" s="25" t="n">
         <f aca="false">IF(B60&lt;=8500,1955,IF(B60&lt;=28000,700+1255*(28000-B60)/19500,IF(B60&lt;=50000,700*(50000-B60)/22000,0)))</f>
-        <v>1588.61706949606</v>
+        <v>1622.83214255631</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B66" s="25" t="n">
         <f aca="false">IF(B64-B65&gt;0,B60*0.02,0)</f>
-        <v>283.856050116763</v>
+        <v>273.223477611983</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B67" s="27" t="n">
         <f aca="false">B60-MAX(0,B64-B65)-B66</f>
-        <v>12233.2189488747</v>
+        <v>11868.7125530057</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B68" s="25" t="n">
         <f aca="false">B67/13</f>
-        <v>941.016842221128</v>
+        <v>912.977888692744</v>
       </c>
     </row>
   </sheetData>
@@ -3570,7 +3587,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3578,7 +3595,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3586,18 +3603,18 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B5" s="23" t="n">
         <f aca="false">Input!$B$21</f>
@@ -3610,7 +3627,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="23" t="n">
         <f aca="false">Input!$B$21*Input!$B$20</f>
@@ -3621,12 +3638,12 @@
         <v>40000</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B7" s="23" t="n">
         <f aca="false">B6*Input!$B$12</f>
@@ -3637,12 +3654,12 @@
         <v>10428</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B8" s="23" t="n">
         <f aca="false">MIN(Input!$B$28,Input!$B$48,Input!$B$52)</f>
@@ -3653,12 +3670,12 @@
         <v>0</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">MAX(0,B6-B7)</f>
@@ -3671,7 +3688,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B10" s="23" t="n">
         <f aca="false">B9*Input!$B$36+IF(MAX(0,Input!$B$52-B8)&lt;=28000,MAX(0,Input!$B$52-B8)*0.23,IF(MAX(0,Input!$B$52-B8)&lt;=50000,6440+(MAX(0,Input!$B$52-B8)-28000)*0.33,13700+(MAX(0,Input!$B$52-B8)-50000)*0.43))</f>
@@ -3682,12 +3699,12 @@
         <v>6958.76</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B11" s="30" t="n">
         <f aca="false">B6-B7+Input!$B$52-B10</f>
@@ -3700,7 +3717,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -3708,7 +3725,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B14" s="23" t="n">
         <f aca="false">B9*Input!$B$36+IF(Input!$B$52&lt;=28000,Input!$B$52*0.23,IF(Input!$B$52&lt;=50000,6440+(Input!$B$52-28000)*0.33,13700+(Input!$B$52-50000)*0.43))</f>
@@ -3721,7 +3738,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B15" s="31" t="n">
         <f aca="false">B14-B10</f>
@@ -3732,12 +3749,12 @@
         <v>0</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B17" s="32"/>
       <c r="C17" s="32"/>
@@ -3745,7 +3762,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="32"/>
@@ -3753,7 +3770,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="32" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="32"/>
@@ -3761,7 +3778,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="32"/>
@@ -3769,7 +3786,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
@@ -3777,7 +3794,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="32"/>
@@ -3785,7 +3802,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="32"/>
@@ -3830,7 +3847,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3840,7 +3857,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3850,25 +3867,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5323,7 +5340,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -5333,7 +5350,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B58" s="25" t="n">
         <f aca="false">INDEX(F5:F54,MATCH(Input!$B$6-1,B5:B54,0))</f>
@@ -5342,7 +5359,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B59" s="25" t="n">
         <f aca="false">Input!$B$31+SUMIF(B5:B54,"&lt;"&amp;Input!$B$6,C5:C54)</f>
@@ -5351,7 +5368,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B60" s="25" t="n">
         <f aca="false">(Input!$B$31*(1+Input!$B$39)^(-Input!$B$7)+SUM(G5:G54))*Input!$B$38</f>
@@ -5360,7 +5377,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B61" s="27" t="n">
         <f aca="false">B58-B60</f>
@@ -5369,7 +5386,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B62" s="11" t="n">
         <f aca="false">B61*Input!$B$43</f>
@@ -5378,7 +5395,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B64" s="32"/>
       <c r="C64" s="32"/>
@@ -5388,7 +5405,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B65" s="32"/>
       <c r="C65" s="32"/>
@@ -5398,7 +5415,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="32" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B66" s="32"/>
       <c r="C66" s="32"/>
@@ -5408,7 +5425,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="32" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B67" s="32"/>
       <c r="C67" s="32"/>
@@ -5452,7 +5469,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5460,7 +5477,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5468,7 +5485,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -5480,12 +5497,12 @@
       </c>
       <c r="B5" s="25" t="n">
         <f aca="false">Previdenza!B60</f>
-        <v>14192.8025058381</v>
+        <v>13661.1738805992</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B6" s="25" t="n">
         <f aca="false">Complementare!B62</f>
@@ -5494,34 +5511,34 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>14192.8025058381</v>
+        <v>13661.1738805992</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">B7/13</f>
-        <v>1091.75403891063</v>
+        <v>1050.85952927686</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B9" s="27" t="n">
         <f aca="false">Previdenza!B67+Complementare!B62</f>
-        <v>12233.2189488747</v>
+        <v>11868.7125530057</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -5529,7 +5546,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">Previdenza!B62</f>
@@ -5538,46 +5555,46 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">IF(B11&gt;0,B5/B11,0)</f>
-        <v>0.340873881447914</v>
+        <v>0.32810555659456</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B13" s="28" t="n">
         <f aca="false">IF(B11&gt;0,B7/B11,0)</f>
-        <v>0.340873881447914</v>
+        <v>0.32810555659456</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B14" s="27" t="n">
         <f aca="false">MAX(0,B11-B7)</f>
-        <v>27443.7184430596</v>
+        <v>27975.3470682985</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B15" s="25" t="n">
         <f aca="false">B14/13</f>
-        <v>2111.05526485073</v>
+        <v>2151.9497744845</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -5585,49 +5602,49 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B20" s="23" t="n">
         <f aca="false">B5</f>
-        <v>14192.8025058381</v>
+        <v>13661.1738805992</v>
       </c>
       <c r="C20" s="34" t="n">
         <f aca="false">IF(B11&gt;0,B5/B11,0)</f>
-        <v>0.340873881447914</v>
+        <v>0.32810555659456</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B21" s="23" t="n">
         <f aca="false">B7</f>
-        <v>14192.8025058381</v>
+        <v>13661.1738805992</v>
       </c>
       <c r="C21" s="34" t="n">
         <f aca="false">IF(B11&gt;0,B7/B11,0)</f>
-        <v>0.340873881447914</v>
+        <v>0.32810555659456</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="32"/>
@@ -5635,7 +5652,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="32" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B24" s="32"/>
       <c r="C24" s="32"/>
@@ -5643,7 +5660,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="32" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
@@ -5651,7 +5668,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
@@ -5659,7 +5676,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="32" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B27" s="32"/>
       <c r="C27" s="32"/>
@@ -5667,7 +5684,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -5675,26 +5692,26 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="33" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B32" s="34" t="n">
         <f aca="false">Input!$B$24-0.01</f>
@@ -5711,7 +5728,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B33" s="34" t="n">
         <f aca="false">Input!$B$14-0.005</f>
@@ -5743,7 +5760,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B35" s="34" t="n">
         <f aca="false">Input!$B$29-Input!$B$30-0.01</f>
@@ -5760,75 +5777,75 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B36" s="23" t="n">
-        <f aca="false">(Input!$B$13*(1+B33)^Input!$B$7+SUMPRODUCT((Previdenza!$A$5:$A$54&lt;Input!$B$7)*((Input!$B$23*(1+B32)^Previdenza!$A$5:$A$54+Input!$B$51-ABS(Input!$B$23*(1+B32)^Previdenza!$A$5:$A$54-Input!$B$51))/2)*Input!$B$12*(1+B33)^(Input!$B$7-1-Previdenza!$A$5:$A$54)))*Input!$B$42*(1-B34)^(Input!$B$7/2)</f>
-        <v>10806.0667563697</v>
+        <f aca="false">(Input!$B$13*(1+B33)^Input!$B$7+SUMPRODUCT((Previdenza!$A$5:$A$54&lt;Input!$B$7)*((Input!$B$23*(1+B32)^Previdenza!$A$5:$A$54+Input!$B$51-ABS(Input!$B$23*(1+B32)^Previdenza!$A$5:$A$54-Input!$B$51))/2)*Input!$B$16*(1+B33)^(Input!$B$7-1-Previdenza!$A$5:$A$54)))*Input!$B$43*((1-B34)/(1-Input!$B$15))^(Input!$B$7/2)</f>
+        <v>10403.7663667322</v>
       </c>
       <c r="C36" s="23" t="n">
-        <f aca="false">(Input!$B$13*(1+C33)^Input!$B$7+SUMPRODUCT((Previdenza!$A$5:$A$54&lt;Input!$B$7)*((Input!$B$23*(1+C32)^Previdenza!$A$5:$A$54+Input!$B$51-ABS(Input!$B$23*(1+C32)^Previdenza!$A$5:$A$54-Input!$B$51))/2)*Input!$B$12*(1+C33)^(Input!$B$7-1-Previdenza!$A$5:$A$54)))*Input!$B$42*(1-C34)^(Input!$B$7/2)</f>
-        <v>14192.8025058381</v>
+        <f aca="false">(Input!$B$13*(1+C33)^Input!$B$7+SUMPRODUCT((Previdenza!$A$5:$A$54&lt;Input!$B$7)*((Input!$B$23*(1+C32)^Previdenza!$A$5:$A$54+Input!$B$51-ABS(Input!$B$23*(1+C32)^Previdenza!$A$5:$A$54-Input!$B$51))/2)*Input!$B$16*(1+C33)^(Input!$B$7-1-Previdenza!$A$5:$A$54)))*Input!$B$43*((1-C34)/(1-Input!$B$15))^(Input!$B$7/2)</f>
+        <v>13661.1738805991</v>
       </c>
       <c r="D36" s="23" t="n">
-        <f aca="false">(Input!$B$13*(1+D33)^Input!$B$7+SUMPRODUCT((Previdenza!$A$5:$A$54&lt;Input!$B$7)*((Input!$B$23*(1+D32)^Previdenza!$A$5:$A$54+Input!$B$51-ABS(Input!$B$23*(1+D32)^Previdenza!$A$5:$A$54-Input!$B$51))/2)*Input!$B$12*(1+D33)^(Input!$B$7-1-Previdenza!$A$5:$A$54)))*Input!$B$42*(1-D34)^(Input!$B$7/2)</f>
-        <v>18360.5950322628</v>
+        <f aca="false">(Input!$B$13*(1+D33)^Input!$B$7+SUMPRODUCT((Previdenza!$A$5:$A$54&lt;Input!$B$7)*((Input!$B$23*(1+D32)^Previdenza!$A$5:$A$54+Input!$B$51-ABS(Input!$B$23*(1+D32)^Previdenza!$A$5:$A$54-Input!$B$51))/2)*Input!$B$16*(1+D33)^(Input!$B$7-1-Previdenza!$A$5:$A$54)))*Input!$B$43*((1-D34)/(1-Input!$B$15))^(Input!$B$7/2)</f>
+        <v>17668.8414083922</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B37" s="23" t="n">
         <f aca="false">B36-MAX(0,IF(B36&lt;=28000,B36*0.23,IF(B36&lt;=50000,6440+(B36-28000)*0.33,13700+(B36-50000)*0.43))-IF(B36&lt;=8500,1955,IF(B36&lt;=28000,700+1255*(28000-B36)/19500,IF(B36&lt;=50000,700*(50000-B36)/22000,0))))-IF(IF(B36&lt;=28000,B36*0.23,IF(B36&lt;=50000,6440+(B36-28000)*0.33,13700+(B36-50000)*0.43))-IF(B36&lt;=8500,1955,IF(B36&lt;=28000,700+1255*(28000-B36)/19500,IF(B36&lt;=50000,700*(50000-B36)/22000,0)))&gt;0,B36*0.02,0)</f>
-        <v>9911.13397603397</v>
+        <v>9635.30032426718</v>
       </c>
       <c r="C37" s="23" t="n">
         <f aca="false">C36-MAX(0,IF(C36&lt;=28000,C36*0.23,IF(C36&lt;=50000,6440+(C36-28000)*0.33,13700+(C36-50000)*0.43))-IF(C36&lt;=8500,1955,IF(C36&lt;=28000,700+1255*(28000-C36)/19500,IF(C36&lt;=50000,700*(50000-C36)/22000,0))))-IF(IF(C36&lt;=28000,C36*0.23,IF(C36&lt;=50000,6440+(C36-28000)*0.33,13700+(C36-50000)*0.43))-IF(C36&lt;=8500,1955,IF(C36&lt;=28000,700+1255*(28000-C36)/19500,IF(C36&lt;=50000,700*(50000-C36)/22000,0)))&gt;0,C36*0.02,0)</f>
-        <v>12233.2189488746</v>
+        <v>11868.7125530057</v>
       </c>
       <c r="D37" s="23" t="n">
         <f aca="false">D36-MAX(0,IF(D36&lt;=28000,D36*0.23,IF(D36&lt;=50000,6440+(D36-28000)*0.33,13700+(D36-50000)*0.43))-IF(D36&lt;=8500,1955,IF(D36&lt;=28000,700+1255*(28000-D36)/19500,IF(D36&lt;=50000,700*(50000-D36)/22000,0))))-IF(IF(D36&lt;=28000,D36*0.23,IF(D36&lt;=50000,6440+(D36-28000)*0.33,13700+(D36-50000)*0.43))-IF(D36&lt;=8500,1955,IF(D36&lt;=28000,700+1255*(28000-D36)/19500,IF(D36&lt;=50000,700*(50000-D36)/22000,0)))&gt;0,D36*0.02,0)</f>
-        <v>15090.8284913515</v>
+        <v>14616.5338271899</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B38" s="23" t="n">
-        <f aca="false">((Input!$B$31*(1+B35)^Input!$B$7+Input!$B$28*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+B35)^(Input!$B$7-Complementare!$A$5:$A$54)))-((Input!$B$31*(1+Input!$B$39)^(-Input!$B$7)+(Input!$B$46+IF(Input!$B$47=1,0,Input!$B$28-Input!$B$46))*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+Input!$B$39)^(Complementare!$A$5:$A$54-Input!$B$7)))*Input!$B$38))*Input!$B$42*(1-B34)^(Input!$B$7/2)</f>
+        <f aca="false">((Input!$B$31*(1+B35)^Input!$B$7+Input!$B$28*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+B35)^(Input!$B$7-Complementare!$A$5:$A$54)))-((Input!$B$31*(1+Input!$B$39)^(-Input!$B$7)+(Input!$B$46+IF(Input!$B$47=1,0,Input!$B$28-Input!$B$46))*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+Input!$B$39)^(Complementare!$A$5:$A$54-Input!$B$7)))*Input!$B$38))*Input!$B$43*((1-B34)/(1-Input!$B$15))^(Input!$B$7/2)</f>
         <v>0</v>
       </c>
       <c r="C38" s="23" t="n">
-        <f aca="false">((Input!$B$31*(1+C35)^Input!$B$7+Input!$B$28*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+C35)^(Input!$B$7-Complementare!$A$5:$A$54)))-((Input!$B$31*(1+Input!$B$39)^(-Input!$B$7)+(Input!$B$46+IF(Input!$B$47=1,0,Input!$B$28-Input!$B$46))*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+Input!$B$39)^(Complementare!$A$5:$A$54-Input!$B$7)))*Input!$B$38))*Input!$B$42*(1-C34)^(Input!$B$7/2)</f>
+        <f aca="false">((Input!$B$31*(1+C35)^Input!$B$7+Input!$B$28*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+C35)^(Input!$B$7-Complementare!$A$5:$A$54)))-((Input!$B$31*(1+Input!$B$39)^(-Input!$B$7)+(Input!$B$46+IF(Input!$B$47=1,0,Input!$B$28-Input!$B$46))*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+Input!$B$39)^(Complementare!$A$5:$A$54-Input!$B$7)))*Input!$B$38))*Input!$B$43*((1-C34)/(1-Input!$B$15))^(Input!$B$7/2)</f>
         <v>0</v>
       </c>
       <c r="D38" s="23" t="n">
-        <f aca="false">((Input!$B$31*(1+D35)^Input!$B$7+Input!$B$28*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+D35)^(Input!$B$7-Complementare!$A$5:$A$54)))-((Input!$B$31*(1+Input!$B$39)^(-Input!$B$7)+(Input!$B$46+IF(Input!$B$47=1,0,Input!$B$28-Input!$B$46))*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+Input!$B$39)^(Complementare!$A$5:$A$54-Input!$B$7)))*Input!$B$38))*Input!$B$42*(1-D34)^(Input!$B$7/2)</f>
+        <f aca="false">((Input!$B$31*(1+D35)^Input!$B$7+Input!$B$28*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+D35)^(Input!$B$7-Complementare!$A$5:$A$54)))-((Input!$B$31*(1+Input!$B$39)^(-Input!$B$7)+(Input!$B$46+IF(Input!$B$47=1,0,Input!$B$28-Input!$B$46))*SUMPRODUCT((Complementare!$A$5:$A$54&lt;Input!$B$7)*(1+Input!$B$39)^(Complementare!$A$5:$A$54-Input!$B$7)))*Input!$B$38))*Input!$B$43*((1-D34)/(1-Input!$B$15))^(Input!$B$7/2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B39" s="30" t="n">
         <f aca="false">B37+B38</f>
-        <v>9911.13397603397</v>
+        <v>9635.30032426718</v>
       </c>
       <c r="C39" s="30" t="n">
         <f aca="false">C37+C38</f>
-        <v>12233.2189488746</v>
+        <v>11868.7125530057</v>
       </c>
       <c r="D39" s="30" t="n">
         <f aca="false">D37+D38</f>
-        <v>15090.8284913515</v>
+        <v>14616.5338271899</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B40" s="23" t="n">
         <f aca="false">Input!$B$55</f>
@@ -5845,41 +5862,41 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B41" s="31" t="n">
         <f aca="false">B40-B39</f>
-        <v>8808.86602396603</v>
+        <v>9084.69967573282</v>
       </c>
       <c r="C41" s="31" t="n">
         <f aca="false">C40-C39</f>
-        <v>6486.78105112536</v>
+        <v>6851.28744699434</v>
       </c>
       <c r="D41" s="31" t="n">
         <f aca="false">D40-D39</f>
-        <v>3629.17150864852</v>
+        <v>4103.46617281006</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="33" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B42" s="34" t="n">
         <f aca="false">IFERROR(B41/B40,0)</f>
-        <v>0.470559082476818</v>
+        <v>0.485293786096839</v>
       </c>
       <c r="C42" s="34" t="n">
         <f aca="false">IFERROR(C41/C40,0)</f>
-        <v>0.346516081790884</v>
+        <v>0.365987577296706</v>
       </c>
       <c r="D42" s="34" t="n">
         <f aca="false">IFERROR(D41/D40,0)</f>
-        <v>0.193865999393618</v>
+        <v>0.21920225282105</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="32" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B44" s="32"/>
       <c r="C44" s="32"/>

--- a/skills/it-pianificazione-autonomi/assets/proiezione-pensione-autonomi.xlsx
+++ b/skills/it-pianificazione-autonomi/assets/proiezione-pensione-autonomi.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Tipo di previdenza</t>
   </si>
   <si>
-    <t xml:space="preserve">informativo; imposta tu l'aliquota sotto</t>
+    <t xml:space="preserve">con 2 (cassa) l'aliquota di computo segue la soggettiva in B12</t>
   </si>
   <si>
     <t xml:space="preserve">Aliquota contributiva (versata)</t>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Aliquota di computo (montante)</t>
   </si>
   <si>
-    <t xml:space="preserve">a montante va solo l'IVS: GS 25% (24% se pensionato o già coperto); cassa: aliquota soggettiva</t>
+    <t xml:space="preserve">calcolato: a montante va solo l'IVS, cioè 25% in Gestione Separata (24% se l'aliquota versata è 24%); per una cassa la soggettiva (B12). Sovrascrivere solo se la cassa accredita a montante anche altro (es. CNPADC)</t>
   </si>
   <si>
     <t xml:space="preserve">Reddito professionale</t>
@@ -1308,7 +1308,8 @@
       <c r="A16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="8" t="n">
+        <f aca="false">IF(Input!$B$11=2,Input!$B$12,MIN(Input!$B$12,0.25))</f>
         <v>0.25</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -5748,6 +5749,7 @@
         <v>19</v>
       </c>
       <c r="B34" s="34" t="n">
+        <f aca="false">Input!$B$15+0.004</f>
         <v>0.022</v>
       </c>
       <c r="C34" s="34" t="n">
@@ -5755,6 +5757,7 @@
         <v>0.018</v>
       </c>
       <c r="D34" s="34" t="n">
+        <f aca="false">MAX(0,Input!$B$15-0.003)</f>
         <v>0.015</v>
       </c>
     </row>

--- a/skills/it-pianificazione-autonomi/assets/proiezione-pensione-autonomi.xlsx
+++ b/skills/it-pianificazione-autonomi/assets/proiezione-pensione-autonomi.xlsx
@@ -246,7 +246,7 @@
     <t xml:space="preserve">Altri redditi IRPEF (no cedolare secca)</t>
   </si>
   <si>
-    <t xml:space="preserve">solo redditi senza detrazioni proprie (affitti a IRPEF ordinaria): con lavoro dipendente o occasionale le detrazioni (art. 13 TUIR) riducono il risparmio, fino ad azzerarlo</t>
+    <t xml:space="preserve">solo redditi senza detrazioni proprie (affitti a IRPEF ordinaria): con lavoro dipendente o occasionale le detrazioni (art. 13 TUIR, dal 2027 art. 13 D.Lgs. 117/2026) riducono il risparmio, fino ad azzerarlo</t>
   </si>
   <si>
     <t xml:space="preserve">Spesa mensile attuale</t>
@@ -345,7 +345,7 @@
     <t xml:space="preserve">IRPEF lorda sulla pensione (scaglioni 2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">Detrazione pensionati (art. 13 c. 3 TUIR)</t>
+    <t xml:space="preserve">Detrazione pensionati (art. 13 c. 3 TUIR, dal 2027 art. 13 c. 3 D.Lgs. 117/2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Addizionali regionali + comunali (~2%, se c'è IRPEF)</t>
